--- a/notes/costs/painting_models_final_2026-09-28.xlsx
+++ b/notes/costs/painting_models_final_2026-09-28.xlsx
@@ -8,14 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Latest (47)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Present &amp; past (156)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Latest (46)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Present &amp; past (145)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Excluded" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Profiles" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest (47)'!$A$1:$O$48</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Present &amp; past (156)'!$A$1:$O$157</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Latest (46)'!$A$1:$O$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Present &amp; past (145)'!$A$1:$O$146</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -522,26 +522,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C4" s="3">
-        <f>'Latest (47)'!K50</f>
+        <f>'Latest (46)'!K49</f>
         <v/>
       </c>
       <c r="D4" s="3">
-        <f>'Latest (47)'!L50</f>
+        <f>'Latest (46)'!L49</f>
         <v/>
       </c>
       <c r="E4" s="3">
-        <f>'Latest (47)'!M50</f>
+        <f>'Latest (46)'!M49</f>
         <v/>
       </c>
       <c r="F4" s="3">
-        <f>'Latest (47)'!N50</f>
+        <f>'Latest (46)'!N49</f>
         <v/>
       </c>
       <c r="G4" s="3">
-        <f>'Latest (47)'!O50</f>
+        <f>'Latest (46)'!O49</f>
         <v/>
       </c>
     </row>
@@ -552,26 +552,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3">
-        <f>'Present &amp; past (156)'!K159</f>
+        <f>'Present &amp; past (145)'!K148</f>
         <v/>
       </c>
       <c r="D5" s="3">
-        <f>'Present &amp; past (156)'!L159</f>
+        <f>'Present &amp; past (145)'!L148</f>
         <v/>
       </c>
       <c r="E5" s="3">
-        <f>'Present &amp; past (156)'!M159</f>
+        <f>'Present &amp; past (145)'!M148</f>
         <v/>
       </c>
       <c r="F5" s="3">
-        <f>'Present &amp; past (156)'!N159</f>
+        <f>'Present &amp; past (145)'!N148</f>
         <v/>
       </c>
       <c r="G5" s="3">
-        <f>'Present &amp; past (156)'!O159</f>
+        <f>'Present &amp; past (145)'!O148</f>
         <v/>
       </c>
     </row>
@@ -633,33 +633,40 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>no OpenAI Pro models; no image-generation models. The sum counts the latest models twice (they're in both sets).</t>
+          <t>no OpenAI Pro models or o1; no image-generation models; no duplicates (o4-mini and -high kept apart; first and last GPT-4o);</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cost = prompt x (8% input + 89% cache read + 3% cache write) + output + images, at list prices; no cache price = input price.</t>
+          <t>no model whose context can't hold a session (under 128K). The sum counts the latest models twice (they're in both sets).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ballpark: x0.5 to x2 (tokenizers, image tokens and thinking length differ). If caching fails, x3 to x5.</t>
+          <t>Cost = prompt x (8% input + 89% cache read + 3% cache write) + output + images, at list prices; no cache price = input price.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Source: https://openrouter.ai/api/v1/models (fetched 2026-09-28); token profiles from our session logs.</t>
+          <t>Ballpark: x0.5 to x2 (tokenizers, image tokens and thinking length differ). If caching fails, x3 to x5.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>Source: https://openrouter.ai/api/v1/models (fetched 2026-09-28); token profiles from our session logs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Yellow rows: models we have painted with.</t>
         </is>
@@ -676,7 +683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O50"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1876,103 +1883,105 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n">
+      <c r="A24" s="6" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>perceptron/perceptron-mk1.5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G24" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="10">
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>google/gemini-3.8-flash</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="J24" s="7" t="n">
+        <v>7.5e-07</v>
+      </c>
+      <c r="K24" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F24+Profiles!$B$8*IF(H24="",F24,H24)+Profiles!$B$10*IF(I24="",F24,I24))+Profiles!$C$3*G24)/1000000+Profiles!$D$3*IF(J24="",0,J24)</f>
         <v/>
       </c>
-      <c r="L24" s="10">
+      <c r="L24" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F24+Profiles!$B$8*IF(H24="",F24,H24)+Profiles!$B$10*IF(I24="",F24,I24))+Profiles!$C$4*G24)/1000000+Profiles!$D$4*IF(J24="",0,J24)</f>
         <v/>
       </c>
-      <c r="M24" s="10">
+      <c r="M24" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F24+Profiles!$B$8*IF(H24="",F24,H24)+Profiles!$B$10*IF(I24="",F24,I24))+Profiles!$C$5*G24)/1000000+Profiles!$D$5*IF(J24="",0,J24)</f>
         <v/>
       </c>
-      <c r="N24" s="10">
+      <c r="N24" s="8">
         <f>K24+L24+M24</f>
         <v/>
       </c>
-      <c r="O24" s="10">
+      <c r="O24" s="8">
         <f>3*N24</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>google/gemini-3.8-flash</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="J25" s="7" t="n">
-        <v>7.5e-07</v>
-      </c>
-      <c r="K25" s="8">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>thinkingmachines/inkling-small</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$3*G25)/1000000+Profiles!$D$3*IF(J25="",0,J25)</f>
         <v/>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$4*G25)/1000000+Profiles!$D$4*IF(J25="",0,J25)</f>
         <v/>
       </c>
-      <c r="M25" s="8">
+      <c r="M25" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$5*G25)/1000000+Profiles!$D$5*IF(J25="",0,J25)</f>
         <v/>
       </c>
-      <c r="N25" s="8">
+      <c r="N25" s="10">
         <f>K25+L25+M25</f>
         <v/>
       </c>
-      <c r="O25" s="8">
+      <c r="O25" s="10">
         <f>3*N25</f>
         <v/>
       </c>
@@ -1983,24 +1992,24 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>thinkingmachines/inkling-small</t>
+          <t>qwen/qwen3.8-27b</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
       <c r="F26" s="9" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="I26" s="9" t="n"/>
       <c r="J26" s="9" t="n"/>
@@ -2031,24 +2040,24 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-27b</t>
+          <t>z-ai/glm-5.3-flashx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
       <c r="F27" s="9" t="n">
-        <v>0.42</v>
+        <v>0.37</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>0.08499999999999999</v>
+        <v>0.09</v>
       </c>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
@@ -2079,26 +2088,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flashx</t>
+          <t>qwen/qwen3.7-plus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="9" t="n">
-        <v>0.37</v>
+        <v>0.32</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I28" s="9" t="n"/>
+        <v>0.064</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>0.4</v>
+      </c>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F28+Profiles!$B$8*IF(H28="",F28,H28)+Profiles!$B$10*IF(I28="",F28,I28))+Profiles!$C$3*G28)/1000000+Profiles!$D$3*IF(J28="",0,J28)</f>
@@ -2127,28 +2138,26 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-plus</t>
+          <t>minimax/minimax-m3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="I29" s="9" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I29" s="9" t="n"/>
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F29+Profiles!$B$8*IF(H29="",F29,H29)+Profiles!$B$10*IF(I29="",F29,I29))+Profiles!$C$3*G29)/1000000+Profiles!$D$3*IF(J29="",0,J29)</f>
@@ -2177,25 +2186,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>minimax/minimax-m3</t>
+          <t>prism-ml/ternary-bonsai-2-27b</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" s="9" t="n">
-        <v>0.3</v>
+        <v>0.075</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>0.06</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10">
@@ -2225,23 +2232,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>prism-ml/ternary-bonsai-2-27b</t>
+          <t>meta/muse-glimmer-30b</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" s="9" t="n">
-        <v>0.075</v>
+        <v>0.3</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H31" s="9" t="n"/>
+        <v>1.2</v>
+      </c>
+      <c r="H31" s="9" t="n">
+        <v>0.04</v>
+      </c>
       <c r="I31" s="9" t="n"/>
       <c r="J31" s="9" t="n"/>
       <c r="K31" s="10">
@@ -2271,27 +2280,35 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>meta/muse-glimmer-30b</t>
+          <t>google/gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Flash Lite line (3.5 is its newest)</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" s="9" t="n">
         <v>0.3</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="H32" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="I32" s="9" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>3e-07</v>
+      </c>
       <c r="K32" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F32+Profiles!$B$8*IF(H32="",F32,H32)+Profiles!$B$10*IF(I32="",F32,I32))+Profiles!$C$3*G32)/1000000+Profiles!$D$3*IF(J32="",0,J32)</f>
         <v/>
@@ -2319,35 +2336,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>google/gemini-3.5-flash-lite</t>
+          <t>deepseek/deepseek-v4-flash-vision-exp</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Flash Lite line (3.5 is its newest)</t>
-        </is>
-      </c>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" s="9" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="G33" s="9" t="n">
-        <v>2.5</v>
+        <v>1.32</v>
       </c>
       <c r="H33" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I33" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>3e-07</v>
-      </c>
+        <v>0.014</v>
+      </c>
+      <c r="I33" s="9" t="n"/>
+      <c r="J33" s="9" t="n"/>
       <c r="K33" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F33+Profiles!$B$8*IF(H33="",F33,H33)+Profiles!$B$10*IF(I33="",F33,I33))+Profiles!$C$3*G33)/1000000+Profiles!$D$3*IF(J33="",0,J33)</f>
         <v/>
@@ -2375,24 +2384,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v4-flash-vision-exp</t>
+          <t>qwen/qwen3.6-35b-a3b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" s="9" t="n">
-        <v>0.44</v>
+        <v>0.15</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>1.32</v>
+        <v>1</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.014</v>
+        <v>0.05</v>
       </c>
       <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="n"/>
@@ -2423,24 +2432,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-35b-a3b</t>
+          <t>stepfun/step-3.7-flash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" s="9" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>1</v>
+        <v>1.15</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="9" t="n"/>
@@ -2466,101 +2475,101 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="n">
+      <c r="A36" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>stepfun/step-3.7-flash</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="10">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>xiaomi/mimo-v2.6-pro</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F36+Profiles!$B$8*IF(H36="",F36,H36)+Profiles!$B$10*IF(I36="",F36,I36))+Profiles!$C$3*G36)/1000000+Profiles!$D$3*IF(J36="",0,J36)</f>
         <v/>
       </c>
-      <c r="L36" s="10">
+      <c r="L36" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F36+Profiles!$B$8*IF(H36="",F36,H36)+Profiles!$B$10*IF(I36="",F36,I36))+Profiles!$C$4*G36)/1000000+Profiles!$D$4*IF(J36="",0,J36)</f>
         <v/>
       </c>
-      <c r="M36" s="10">
+      <c r="M36" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F36+Profiles!$B$8*IF(H36="",F36,H36)+Profiles!$B$10*IF(I36="",F36,I36))+Profiles!$C$5*G36)/1000000+Profiles!$D$5*IF(J36="",0,J36)</f>
         <v/>
       </c>
-      <c r="N36" s="10">
+      <c r="N36" s="8">
         <f>K36+L36+M36</f>
         <v/>
       </c>
-      <c r="O36" s="10">
+      <c r="O36" s="8">
         <f>3*N36</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="n">
+      <c r="A37" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>xiaomi/mimo-v2.6-pro</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="D37" s="6" t="inlineStr"/>
-      <c r="E37" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="G37" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="I37" s="7" t="n"/>
-      <c r="J37" s="7" t="n"/>
-      <c r="K37" s="8">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>google/gemma-4-31b-it</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" s="9" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G37" s="9" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H37" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F37+Profiles!$B$8*IF(H37="",F37,H37)+Profiles!$B$10*IF(I37="",F37,I37))+Profiles!$C$3*G37)/1000000+Profiles!$D$3*IF(J37="",0,J37)</f>
         <v/>
       </c>
-      <c r="L37" s="8">
+      <c r="L37" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F37+Profiles!$B$8*IF(H37="",F37,H37)+Profiles!$B$10*IF(I37="",F37,I37))+Profiles!$C$4*G37)/1000000+Profiles!$D$4*IF(J37="",0,J37)</f>
         <v/>
       </c>
-      <c r="M37" s="8">
+      <c r="M37" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F37+Profiles!$B$8*IF(H37="",F37,H37)+Profiles!$B$10*IF(I37="",F37,I37))+Profiles!$C$5*G37)/1000000+Profiles!$D$5*IF(J37="",0,J37)</f>
         <v/>
       </c>
-      <c r="N37" s="8">
+      <c r="N37" s="10">
         <f>K37+L37+M37</f>
         <v/>
       </c>
-      <c r="O37" s="8">
+      <c r="O37" s="10">
         <f>3*N37</f>
         <v/>
       </c>
@@ -2571,12 +2580,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>google/gemma-4-31b-it</t>
+          <t>google/gemma-4-26b-a4b-it</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -2585,7 +2594,7 @@
         <v>0.09</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.34</v>
+        <v>0.3</v>
       </c>
       <c r="H38" s="9" t="n">
         <v>0.05</v>
@@ -2614,101 +2623,103 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="n">
+      <c r="A39" s="6" t="n">
         <v>38</v>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>google/gemma-4-26b-a4b-it</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="10">
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I39" s="7" t="n"/>
+      <c r="J39" s="7" t="n"/>
+      <c r="K39" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F39+Profiles!$B$8*IF(H39="",F39,H39)+Profiles!$B$10*IF(I39="",F39,I39))+Profiles!$C$3*G39)/1000000+Profiles!$D$3*IF(J39="",0,J39)</f>
         <v/>
       </c>
-      <c r="L39" s="10">
+      <c r="L39" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F39+Profiles!$B$8*IF(H39="",F39,H39)+Profiles!$B$10*IF(I39="",F39,I39))+Profiles!$C$4*G39)/1000000+Profiles!$D$4*IF(J39="",0,J39)</f>
         <v/>
       </c>
-      <c r="M39" s="10">
+      <c r="M39" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F39+Profiles!$B$8*IF(H39="",F39,H39)+Profiles!$B$10*IF(I39="",F39,I39))+Profiles!$C$5*G39)/1000000+Profiles!$D$5*IF(J39="",0,J39)</f>
         <v/>
       </c>
-      <c r="N39" s="10">
+      <c r="N39" s="8">
         <f>K39+L39+M39</f>
         <v/>
       </c>
-      <c r="O39" s="10">
+      <c r="O39" s="8">
         <f>3*N39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n">
+      <c r="A40" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>z-ai/glm-5.3-flash</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="n">
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H40" s="7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I40" s="7" t="n"/>
-      <c r="J40" s="7" t="n"/>
-      <c r="K40" s="8">
+      <c r="G40" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I40" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F40+Profiles!$B$8*IF(H40="",F40,H40)+Profiles!$B$10*IF(I40="",F40,I40))+Profiles!$C$3*G40)/1000000+Profiles!$D$3*IF(J40="",0,J40)</f>
         <v/>
       </c>
-      <c r="L40" s="8">
+      <c r="L40" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F40+Profiles!$B$8*IF(H40="",F40,H40)+Profiles!$B$10*IF(I40="",F40,I40))+Profiles!$C$4*G40)/1000000+Profiles!$D$4*IF(J40="",0,J40)</f>
         <v/>
       </c>
-      <c r="M40" s="8">
+      <c r="M40" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F40+Profiles!$B$8*IF(H40="",F40,H40)+Profiles!$B$10*IF(I40="",F40,I40))+Profiles!$C$5*G40)/1000000+Profiles!$D$5*IF(J40="",0,J40)</f>
         <v/>
       </c>
-      <c r="N40" s="8">
+      <c r="N40" s="10">
         <f>K40+L40+M40</f>
         <v/>
       </c>
-      <c r="O40" s="8">
+      <c r="O40" s="10">
         <f>3*N40</f>
         <v/>
       </c>
@@ -2719,12 +2730,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-flash</t>
+          <t>qwen/qwen3.8-omni-flash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -2738,9 +2749,7 @@
       <c r="H41" s="9" t="n">
         <v>0.016</v>
       </c>
-      <c r="I41" s="9" t="n">
-        <v>0.2</v>
-      </c>
+      <c r="I41" s="9" t="n"/>
       <c r="J41" s="9" t="n"/>
       <c r="K41" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F41+Profiles!$B$8*IF(H41="",F41,H41)+Profiles!$B$10*IF(I41="",F41,I41))+Profiles!$C$3*G41)/1000000+Profiles!$D$3*IF(J41="",0,J41)</f>
@@ -2764,103 +2773,103 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>qwen/qwen3.8-omni-flash</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>openai/gpt-6-luna</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I42" s="7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="8">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$3*G42)/1000000+Profiles!$D$3*IF(J42="",0,J42)</f>
+        <v/>
+      </c>
+      <c r="L42" s="8">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$4*G42)/1000000+Profiles!$D$4*IF(J42="",0,J42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="8">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$5*G42)/1000000+Profiles!$D$5*IF(J42="",0,J42)</f>
+        <v/>
+      </c>
+      <c r="N42" s="8">
+        <f>K42+L42+M42</f>
+        <v/>
+      </c>
+      <c r="O42" s="8">
+        <f>3*N42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>xiaomi/mimo-v2.6-flash</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$3*G42)/1000000+Profiles!$D$3*IF(J42="",0,J42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$4*G42)/1000000+Profiles!$D$4*IF(J42="",0,J42)</f>
-        <v/>
-      </c>
-      <c r="M42" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$5*G42)/1000000+Profiles!$D$5*IF(J42="",0,J42)</f>
-        <v/>
-      </c>
-      <c r="N42" s="10">
-        <f>K42+L42+M42</f>
-        <v/>
-      </c>
-      <c r="O42" s="10">
-        <f>3*N42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>openai/gpt-6-luna</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I43" s="7" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="8">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>0.0028</v>
+      </c>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F43+Profiles!$B$8*IF(H43="",F43,H43)+Profiles!$B$10*IF(I43="",F43,I43))+Profiles!$C$3*G43)/1000000+Profiles!$D$3*IF(J43="",0,J43)</f>
         <v/>
       </c>
-      <c r="L43" s="8">
+      <c r="L43" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F43+Profiles!$B$8*IF(H43="",F43,H43)+Profiles!$B$10*IF(I43="",F43,I43))+Profiles!$C$4*G43)/1000000+Profiles!$D$4*IF(J43="",0,J43)</f>
         <v/>
       </c>
-      <c r="M43" s="8">
+      <c r="M43" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F43+Profiles!$B$8*IF(H43="",F43,H43)+Profiles!$B$10*IF(I43="",F43,I43))+Profiles!$C$5*G43)/1000000+Profiles!$D$5*IF(J43="",0,J43)</f>
         <v/>
       </c>
-      <c r="N43" s="8">
+      <c r="N43" s="10">
         <f>K43+L43+M43</f>
         <v/>
       </c>
-      <c r="O43" s="8">
+      <c r="O43" s="10">
         <f>3*N43</f>
         <v/>
       </c>
@@ -2871,24 +2880,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>xiaomi/mimo-v2.6-flash</t>
+          <t>meta/muse-spark-1.3-contributor</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>cheap contributor tier (check its data terms)</t>
+        </is>
+      </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" s="9" t="n">
-        <v>0.14</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.0028</v>
+        <v>0.002</v>
       </c>
       <c r="I44" s="9" t="n"/>
       <c r="J44" s="9" t="n"/>
@@ -2914,240 +2927,188 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="n">
+      <c r="A45" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>meta/muse-spark-1.3-contributor</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>cheap contributor tier (check its data terms)</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" s="9" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="10">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4.1-flash</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I45" s="7" t="n"/>
+      <c r="J45" s="7" t="n"/>
+      <c r="K45" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F45+Profiles!$B$8*IF(H45="",F45,H45)+Profiles!$B$10*IF(I45="",F45,I45))+Profiles!$C$3*G45)/1000000+Profiles!$D$3*IF(J45="",0,J45)</f>
         <v/>
       </c>
-      <c r="L45" s="10">
+      <c r="L45" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F45+Profiles!$B$8*IF(H45="",F45,H45)+Profiles!$B$10*IF(I45="",F45,I45))+Profiles!$C$4*G45)/1000000+Profiles!$D$4*IF(J45="",0,J45)</f>
         <v/>
       </c>
-      <c r="M45" s="10">
+      <c r="M45" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F45+Profiles!$B$8*IF(H45="",F45,H45)+Profiles!$B$10*IF(I45="",F45,I45))+Profiles!$C$5*G45)/1000000+Profiles!$D$5*IF(J45="",0,J45)</f>
         <v/>
       </c>
-      <c r="N45" s="10">
+      <c r="N45" s="8">
         <f>K45+L45+M45</f>
         <v/>
       </c>
-      <c r="O45" s="10">
+      <c r="O45" s="8">
         <f>3*N45</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n">
+      <c r="A46" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>deepseek/deepseek-v4.1-flash</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>inclusionai/ling-3.0-flash-vl</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr"/>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" s="9" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>0.0616</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>0.004200000000000001</v>
+      </c>
+      <c r="I46" s="9" t="n"/>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="10">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F46+Profiles!$B$8*IF(H46="",F46,H46)+Profiles!$B$10*IF(I46="",F46,I46))+Profiles!$C$3*G46)/1000000+Profiles!$D$3*IF(J46="",0,J46)</f>
+        <v/>
+      </c>
+      <c r="L46" s="10">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F46+Profiles!$B$8*IF(H46="",F46,H46)+Profiles!$B$10*IF(I46="",F46,I46))+Profiles!$C$4*G46)/1000000+Profiles!$D$4*IF(J46="",0,J46)</f>
+        <v/>
+      </c>
+      <c r="M46" s="10">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F46+Profiles!$B$8*IF(H46="",F46,H46)+Profiles!$B$10*IF(I46="",F46,I46))+Profiles!$C$5*G46)/1000000+Profiles!$D$5*IF(J46="",0,J46)</f>
+        <v/>
+      </c>
+      <c r="N46" s="10">
+        <f>K46+L46+M46</f>
+        <v/>
+      </c>
+      <c r="O46" s="10">
+        <f>3*N46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>stealth/space-bunny-alpha</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>free (stealth)</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F46" s="7" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G46" s="7" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H46" s="7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I46" s="7" t="n"/>
-      <c r="J46" s="7" t="n"/>
-      <c r="K46" s="8">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F46+Profiles!$B$8*IF(H46="",F46,H46)+Profiles!$B$10*IF(I46="",F46,I46))+Profiles!$C$3*G46)/1000000+Profiles!$D$3*IF(J46="",0,J46)</f>
-        <v/>
-      </c>
-      <c r="L46" s="8">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F46+Profiles!$B$8*IF(H46="",F46,H46)+Profiles!$B$10*IF(I46="",F46,I46))+Profiles!$C$4*G46)/1000000+Profiles!$D$4*IF(J46="",0,J46)</f>
-        <v/>
-      </c>
-      <c r="M46" s="8">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F46+Profiles!$B$8*IF(H46="",F46,H46)+Profiles!$B$10*IF(I46="",F46,I46))+Profiles!$C$5*G46)/1000000+Profiles!$D$5*IF(J46="",0,J46)</f>
-        <v/>
-      </c>
-      <c r="N46" s="8">
-        <f>K46+L46+M46</f>
-        <v/>
-      </c>
-      <c r="O46" s="8">
-        <f>3*N46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>inclusionai/ling-3.0-flash-vl</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" s="9" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="G47" s="9" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="H47" s="9" t="n">
-        <v>0.004200000000000001</v>
-      </c>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="10">
+      <c r="F47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="7" t="n"/>
+      <c r="I47" s="7" t="n"/>
+      <c r="J47" s="7" t="n"/>
+      <c r="K47" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F47+Profiles!$B$8*IF(H47="",F47,H47)+Profiles!$B$10*IF(I47="",F47,I47))+Profiles!$C$3*G47)/1000000+Profiles!$D$3*IF(J47="",0,J47)</f>
         <v/>
       </c>
-      <c r="L47" s="10">
+      <c r="L47" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F47+Profiles!$B$8*IF(H47="",F47,H47)+Profiles!$B$10*IF(I47="",F47,I47))+Profiles!$C$4*G47)/1000000+Profiles!$D$4*IF(J47="",0,J47)</f>
         <v/>
       </c>
-      <c r="M47" s="10">
+      <c r="M47" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F47+Profiles!$B$8*IF(H47="",F47,H47)+Profiles!$B$10*IF(I47="",F47,I47))+Profiles!$C$5*G47)/1000000+Profiles!$D$5*IF(J47="",0,J47)</f>
         <v/>
       </c>
-      <c r="N47" s="10">
+      <c r="N47" s="8">
         <f>K47+L47+M47</f>
         <v/>
       </c>
-      <c r="O47" s="10">
+      <c r="O47" s="8">
         <f>3*N47</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>stealth/space-bunny-alpha</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>free (stealth)</t>
-        </is>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="7" t="n"/>
-      <c r="I48" s="7" t="n"/>
-      <c r="J48" s="7" t="n"/>
-      <c r="K48" s="8">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F48+Profiles!$B$8*IF(H48="",F48,H48)+Profiles!$B$10*IF(I48="",F48,I48))+Profiles!$C$3*G48)/1000000+Profiles!$D$3*IF(J48="",0,J48)</f>
-        <v/>
-      </c>
-      <c r="L48" s="8">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F48+Profiles!$B$8*IF(H48="",F48,H48)+Profiles!$B$10*IF(I48="",F48,I48))+Profiles!$C$4*G48)/1000000+Profiles!$D$4*IF(J48="",0,J48)</f>
-        <v/>
-      </c>
-      <c r="M48" s="8">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F48+Profiles!$B$8*IF(H48="",F48,H48)+Profiles!$B$10*IF(I48="",F48,I48))+Profiles!$C$5*G48)/1000000+Profiles!$D$5*IF(J48="",0,J48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="8">
-        <f>K48+L48+M48</f>
-        <v/>
-      </c>
-      <c r="O48" s="8">
-        <f>3*N48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" s="4" t="inlineStr">
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="K50" s="11">
-        <f>SUM(K2:K48)</f>
-        <v/>
-      </c>
-      <c r="L50" s="11">
-        <f>SUM(L2:L48)</f>
-        <v/>
-      </c>
-      <c r="M50" s="11">
-        <f>SUM(M2:M48)</f>
-        <v/>
-      </c>
-      <c r="N50" s="11">
-        <f>SUM(N2:N48)</f>
-        <v/>
-      </c>
-      <c r="O50" s="11">
-        <f>SUM(O2:O48)</f>
+      <c r="K49" s="11">
+        <f>SUM(K2:K47)</f>
+        <v/>
+      </c>
+      <c r="L49" s="11">
+        <f>SUM(L2:L47)</f>
+        <v/>
+      </c>
+      <c r="M49" s="11">
+        <f>SUM(M2:M47)</f>
+        <v/>
+      </c>
+      <c r="N49" s="11">
+        <f>SUM(N2:N47)</f>
+        <v/>
+      </c>
+      <c r="O49" s="11">
+        <f>SUM(O2:O47)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O48"/>
+  <autoFilter ref="A1:O47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3158,7 +3119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O159"/>
+  <dimension ref="A1:O148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3261,23 +3222,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>perceptron/perceptron-mk1.5</t>
+          <t>fireworks/ember-1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kimi K3 fine-tune with shorter reasoning (likely cheaper than shown)</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" s="9" t="n">
-        <v>0.15</v>
+        <v>3</v>
       </c>
       <c r="G2" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H2" s="9" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="H2" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="I2" s="9" t="n"/>
       <c r="J2" s="9" t="n"/>
       <c r="K2" s="10">
@@ -3307,28 +3274,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fireworks/ember-1</t>
+          <t>qwen/qwen3.8-max-prime</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Kimi K3 fine-tune with shorter reasoning (likely cheaper than shown)</t>
-        </is>
-      </c>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G3" s="9" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H3" s="9" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
@@ -3354,309 +3317,309 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>qwen/qwen3.8-max-prime</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>stealth/space-bunny-alpha</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" s="9" t="n">
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>free (stealth)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="7" t="n"/>
+      <c r="I4" s="7" t="n"/>
+      <c r="J4" s="7" t="n"/>
+      <c r="K4" s="8">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F4+Profiles!$B$8*IF(H4="",F4,H4)+Profiles!$B$10*IF(I4="",F4,I4))+Profiles!$C$3*G4)/1000000+Profiles!$D$3*IF(J4="",0,J4)</f>
+        <v/>
+      </c>
+      <c r="L4" s="8">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F4+Profiles!$B$8*IF(H4="",F4,H4)+Profiles!$B$10*IF(I4="",F4,I4))+Profiles!$C$4*G4)/1000000+Profiles!$D$4*IF(J4="",0,J4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="8">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F4+Profiles!$B$8*IF(H4="",F4,H4)+Profiles!$B$10*IF(I4="",F4,I4))+Profiles!$C$5*G4)/1000000+Profiles!$D$5*IF(J4="",0,J4)</f>
+        <v/>
+      </c>
+      <c r="N4" s="8">
+        <f>K4+L4+M4</f>
+        <v/>
+      </c>
+      <c r="O4" s="8">
+        <f>3*N4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="G4" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H4" s="9" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>cohere/command-a-plus</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="9" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="10">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F5+Profiles!$B$8*IF(H5="",F5,H5)+Profiles!$B$10*IF(I5="",F5,I5))+Profiles!$C$3*G5)/1000000+Profiles!$D$3*IF(J5="",0,J5)</f>
+        <v/>
+      </c>
+      <c r="L5" s="10">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F5+Profiles!$B$8*IF(H5="",F5,H5)+Profiles!$B$10*IF(I5="",F5,I5))+Profiles!$C$4*G5)/1000000+Profiles!$D$4*IF(J5="",0,J5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="10">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F5+Profiles!$B$8*IF(H5="",F5,H5)+Profiles!$B$10*IF(I5="",F5,I5))+Profiles!$C$5*G5)/1000000+Profiles!$D$5*IF(J5="",0,J5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="10">
+        <f>K5+L5+M5</f>
+        <v/>
+      </c>
+      <c r="O5" s="10">
+        <f>3*N5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>openai/gpt-6-luna</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="G6" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F4+Profiles!$B$8*IF(H4="",F4,H4)+Profiles!$B$10*IF(I4="",F4,I4))+Profiles!$C$3*G4)/1000000+Profiles!$D$3*IF(J4="",0,J4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F4+Profiles!$B$8*IF(H4="",F4,H4)+Profiles!$B$10*IF(I4="",F4,I4))+Profiles!$C$4*G4)/1000000+Profiles!$D$4*IF(J4="",0,J4)</f>
-        <v/>
-      </c>
-      <c r="M4" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F4+Profiles!$B$8*IF(H4="",F4,H4)+Profiles!$B$10*IF(I4="",F4,I4))+Profiles!$C$5*G4)/1000000+Profiles!$D$5*IF(J4="",0,J4)</f>
-        <v/>
-      </c>
-      <c r="N4" s="10">
-        <f>K4+L4+M4</f>
-        <v/>
-      </c>
-      <c r="O4" s="10">
-        <f>3*N4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="H6" s="7" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="8">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F6+Profiles!$B$8*IF(H6="",F6,H6)+Profiles!$B$10*IF(I6="",F6,I6))+Profiles!$C$3*G6)/1000000+Profiles!$D$3*IF(J6="",0,J6)</f>
+        <v/>
+      </c>
+      <c r="L6" s="8">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F6+Profiles!$B$8*IF(H6="",F6,H6)+Profiles!$B$10*IF(I6="",F6,I6))+Profiles!$C$4*G6)/1000000+Profiles!$D$4*IF(J6="",0,J6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="8">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F6+Profiles!$B$8*IF(H6="",F6,H6)+Profiles!$B$10*IF(I6="",F6,I6))+Profiles!$C$5*G6)/1000000+Profiles!$D$5*IF(J6="",0,J6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="8">
+        <f>K6+L6+M6</f>
+        <v/>
+      </c>
+      <c r="O6" s="8">
+        <f>3*N6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openai/gpt-6-sol</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="10">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F7+Profiles!$B$8*IF(H7="",F7,H7)+Profiles!$B$10*IF(I7="",F7,I7))+Profiles!$C$3*G7)/1000000+Profiles!$D$3*IF(J7="",0,J7)</f>
+        <v/>
+      </c>
+      <c r="L7" s="10">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F7+Profiles!$B$8*IF(H7="",F7,H7)+Profiles!$B$10*IF(I7="",F7,I7))+Profiles!$C$4*G7)/1000000+Profiles!$D$4*IF(J7="",0,J7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="10">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F7+Profiles!$B$8*IF(H7="",F7,H7)+Profiles!$B$10*IF(I7="",F7,I7))+Profiles!$C$5*G7)/1000000+Profiles!$D$5*IF(J7="",0,J7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="10">
+        <f>K7+L7+M7</f>
+        <v/>
+      </c>
+      <c r="O7" s="10">
+        <f>3*N7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>anthropic/claude-opus-5.5</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>stealth/space-bunny-alpha</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>free (stealth)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="7" t="n"/>
-      <c r="I5" s="7" t="n"/>
-      <c r="J5" s="7" t="n"/>
-      <c r="K5" s="8">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F5+Profiles!$B$8*IF(H5="",F5,H5)+Profiles!$B$10*IF(I5="",F5,I5))+Profiles!$C$3*G5)/1000000+Profiles!$D$3*IF(J5="",0,J5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="8">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F5+Profiles!$B$8*IF(H5="",F5,H5)+Profiles!$B$10*IF(I5="",F5,I5))+Profiles!$C$4*G5)/1000000+Profiles!$D$4*IF(J5="",0,J5)</f>
-        <v/>
-      </c>
-      <c r="M5" s="8">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F5+Profiles!$B$8*IF(H5="",F5,H5)+Profiles!$B$10*IF(I5="",F5,I5))+Profiles!$C$5*G5)/1000000+Profiles!$D$5*IF(J5="",0,J5)</f>
-        <v/>
-      </c>
-      <c r="N5" s="8">
-        <f>K5+L5+M5</f>
-        <v/>
-      </c>
-      <c r="O5" s="8">
-        <f>3*N5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="G8" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>cohere/command-a-plus</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G6" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H6" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F6+Profiles!$B$8*IF(H6="",F6,H6)+Profiles!$B$10*IF(I6="",F6,I6))+Profiles!$C$3*G6)/1000000+Profiles!$D$3*IF(J6="",0,J6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F6+Profiles!$B$8*IF(H6="",F6,H6)+Profiles!$B$10*IF(I6="",F6,I6))+Profiles!$C$4*G6)/1000000+Profiles!$D$4*IF(J6="",0,J6)</f>
-        <v/>
-      </c>
-      <c r="M6" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F6+Profiles!$B$8*IF(H6="",F6,H6)+Profiles!$B$10*IF(I6="",F6,I6))+Profiles!$C$5*G6)/1000000+Profiles!$D$5*IF(J6="",0,J6)</f>
-        <v/>
-      </c>
-      <c r="N6" s="10">
-        <f>K6+L6+M6</f>
-        <v/>
-      </c>
-      <c r="O6" s="10">
-        <f>3*N6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>openai/gpt-6-luna</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="J7" s="7" t="n"/>
-      <c r="K7" s="8">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F7+Profiles!$B$8*IF(H7="",F7,H7)+Profiles!$B$10*IF(I7="",F7,I7))+Profiles!$C$3*G7)/1000000+Profiles!$D$3*IF(J7="",0,J7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="8">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F7+Profiles!$B$8*IF(H7="",F7,H7)+Profiles!$B$10*IF(I7="",F7,I7))+Profiles!$C$4*G7)/1000000+Profiles!$D$4*IF(J7="",0,J7)</f>
-        <v/>
-      </c>
-      <c r="M7" s="8">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F7+Profiles!$B$8*IF(H7="",F7,H7)+Profiles!$B$10*IF(I7="",F7,I7))+Profiles!$C$5*G7)/1000000+Profiles!$D$5*IF(J7="",0,J7)</f>
-        <v/>
-      </c>
-      <c r="N7" s="8">
-        <f>K7+L7+M7</f>
-        <v/>
-      </c>
-      <c r="O7" s="8">
-        <f>3*N7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>openai/gpt-6-sol</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I8" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="10">
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F8+Profiles!$B$8*IF(H8="",F8,H8)+Profiles!$B$10*IF(I8="",F8,I8))+Profiles!$C$3*G8)/1000000+Profiles!$D$3*IF(J8="",0,J8)</f>
         <v/>
       </c>
-      <c r="L8" s="10">
+      <c r="L8" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F8+Profiles!$B$8*IF(H8="",F8,H8)+Profiles!$B$10*IF(I8="",F8,I8))+Profiles!$C$4*G8)/1000000+Profiles!$D$4*IF(J8="",0,J8)</f>
         <v/>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F8+Profiles!$B$8*IF(H8="",F8,H8)+Profiles!$B$10*IF(I8="",F8,I8))+Profiles!$C$5*G8)/1000000+Profiles!$D$5*IF(J8="",0,J8)</f>
         <v/>
       </c>
-      <c r="N8" s="10">
+      <c r="N8" s="8">
         <f>K8+L8+M8</f>
         <v/>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="8">
         <f>3*N8</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="n">
+      <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>anthropic/claude-opus-5.5</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="8">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>xiaomi/mimo-v2.6-pro-ultraspeed</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="9" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F9+Profiles!$B$8*IF(H9="",F9,H9)+Profiles!$B$10*IF(I9="",F9,I9))+Profiles!$C$3*G9)/1000000+Profiles!$D$3*IF(J9="",0,J9)</f>
         <v/>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F9+Profiles!$B$8*IF(H9="",F9,H9)+Profiles!$B$10*IF(I9="",F9,I9))+Profiles!$C$4*G9)/1000000+Profiles!$D$4*IF(J9="",0,J9)</f>
         <v/>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F9+Profiles!$B$8*IF(H9="",F9,H9)+Profiles!$B$10*IF(I9="",F9,I9))+Profiles!$C$5*G9)/1000000+Profiles!$D$5*IF(J9="",0,J9)</f>
         <v/>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="10">
         <f>K9+L9+M9</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="10">
         <f>3*N9</f>
         <v/>
       </c>
@@ -3667,7 +3630,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>xiaomi/mimo-v2.6-pro-ultraspeed</t>
+          <t>xiaomi/mimo-v2.6-flash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3678,13 +3641,13 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" s="9" t="n">
-        <v>4.35</v>
+        <v>0.14</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>8.699999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>0.036</v>
+        <v>0.0028</v>
       </c>
       <c r="I10" s="9" t="n"/>
       <c r="J10" s="9" t="n"/>
@@ -3710,101 +3673,101 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="n">
+      <c r="A11" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>xiaomi/mimo-v2.6-flash</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>xiaomi/mimo-v2.6-pro</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="H11" s="9" t="n">
-        <v>0.0028</v>
-      </c>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="10">
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>0.0036</v>
+      </c>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F11+Profiles!$B$8*IF(H11="",F11,H11)+Profiles!$B$10*IF(I11="",F11,I11))+Profiles!$C$3*G11)/1000000+Profiles!$D$3*IF(J11="",0,J11)</f>
         <v/>
       </c>
-      <c r="L11" s="10">
+      <c r="L11" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F11+Profiles!$B$8*IF(H11="",F11,H11)+Profiles!$B$10*IF(I11="",F11,I11))+Profiles!$C$4*G11)/1000000+Profiles!$D$4*IF(J11="",0,J11)</f>
         <v/>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F11+Profiles!$B$8*IF(H11="",F11,H11)+Profiles!$B$10*IF(I11="",F11,I11))+Profiles!$C$5*G11)/1000000+Profiles!$D$5*IF(J11="",0,J11)</f>
         <v/>
       </c>
-      <c r="N11" s="10">
+      <c r="N11" s="8">
         <f>K11+L11+M11</f>
         <v/>
       </c>
-      <c r="O11" s="10">
+      <c r="O11" s="8">
         <f>3*N11</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="n">
+      <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>xiaomi/mimo-v2.6-pro</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>x-ai/grok-4.7</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="G12" s="7" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.0036</v>
-      </c>
-      <c r="I12" s="7" t="n"/>
-      <c r="J12" s="7" t="n"/>
-      <c r="K12" s="8">
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" s="9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G12" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I12" s="9" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F12+Profiles!$B$8*IF(H12="",F12,H12)+Profiles!$B$10*IF(I12="",F12,I12))+Profiles!$C$3*G12)/1000000+Profiles!$D$3*IF(J12="",0,J12)</f>
         <v/>
       </c>
-      <c r="L12" s="8">
+      <c r="L12" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F12+Profiles!$B$8*IF(H12="",F12,H12)+Profiles!$B$10*IF(I12="",F12,I12))+Profiles!$C$4*G12)/1000000+Profiles!$D$4*IF(J12="",0,J12)</f>
         <v/>
       </c>
-      <c r="M12" s="8">
+      <c r="M12" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F12+Profiles!$B$8*IF(H12="",F12,H12)+Profiles!$B$10*IF(I12="",F12,I12))+Profiles!$C$5*G12)/1000000+Profiles!$D$5*IF(J12="",0,J12)</f>
         <v/>
       </c>
-      <c r="N12" s="8">
+      <c r="N12" s="10">
         <f>K12+L12+M12</f>
         <v/>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="10">
         <f>3*N12</f>
         <v/>
       </c>
@@ -3815,7 +3778,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.7</t>
+          <t>qwen/qwen3.8-omni-flash</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3826,13 +3789,13 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" s="9" t="n">
-        <v>1.6</v>
+        <v>0.15</v>
       </c>
       <c r="G13" s="9" t="n">
-        <v>4.8</v>
+        <v>0.47</v>
       </c>
       <c r="H13" s="9" t="n">
-        <v>0.4</v>
+        <v>0.016</v>
       </c>
       <c r="I13" s="9" t="n"/>
       <c r="J13" s="9" t="n"/>
@@ -3863,25 +3826,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-omni-flash</t>
+          <t>prism-ml/ternary-bonsai-2-27b</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" s="9" t="n">
-        <v>0.15</v>
+        <v>0.075</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H14" s="9" t="n">
-        <v>0.016</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="n"/>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10">
@@ -3911,7 +3872,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>prism-ml/ternary-bonsai-2-27b</t>
+          <t>z-ai/glm-5.3-flashx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3922,12 +3883,14 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
       <c r="F15" s="9" t="n">
-        <v>0.075</v>
+        <v>0.37</v>
       </c>
       <c r="G15" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H15" s="9" t="n"/>
+        <v>1.25</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0.09</v>
+      </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="10">
@@ -3957,7 +3920,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>z-ai/glm-5.3-flashx</t>
+          <t>unbiased/pareto</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3965,16 +3928,20 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>ensemble (several unnamed models per request): kept on purpose</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" s="9" t="n">
-        <v>0.37</v>
+        <v>2.5</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>1.25</v>
+        <v>7.5</v>
       </c>
       <c r="H16" s="9" t="n">
-        <v>0.09</v>
+        <v>0.25</v>
       </c>
       <c r="I16" s="9" t="n"/>
       <c r="J16" s="9" t="n"/>
@@ -4005,28 +3972,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>unbiased/pareto</t>
+          <t>inclusionai/ling-3.0-flash-vl</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>ensemble (several unnamed models per request): kept on purpose</t>
-        </is>
-      </c>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" s="9" t="n">
-        <v>2.5</v>
+        <v>0.021</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>7.5</v>
+        <v>0.0616</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>0.25</v>
+        <v>0.004200000000000001</v>
       </c>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n"/>
@@ -4052,49 +4015,53 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="n">
+      <c r="A18" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>inclusionai/ling-3.0-flash-vl</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>deepseek/deepseek-v4.1-flash</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" s="9" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="G18" s="9" t="n">
-        <v>0.0616</v>
-      </c>
-      <c r="H18" s="9" t="n">
-        <v>0.004200000000000001</v>
-      </c>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="10">
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>0.035</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F18+Profiles!$B$8*IF(H18="",F18,H18)+Profiles!$B$10*IF(I18="",F18,I18))+Profiles!$C$3*G18)/1000000+Profiles!$D$3*IF(J18="",0,J18)</f>
         <v/>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F18+Profiles!$B$8*IF(H18="",F18,H18)+Profiles!$B$10*IF(I18="",F18,I18))+Profiles!$C$4*G18)/1000000+Profiles!$D$4*IF(J18="",0,J18)</f>
         <v/>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F18+Profiles!$B$8*IF(H18="",F18,H18)+Profiles!$B$10*IF(I18="",F18,I18))+Profiles!$C$5*G18)/1000000+Profiles!$D$5*IF(J18="",0,J18)</f>
         <v/>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="8">
         <f>K18+L18+M18</f>
         <v/>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="8">
         <f>3*N18</f>
         <v/>
       </c>
@@ -4105,12 +4072,12 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v4.1-flash</t>
+          <t>openai/gpt-6-astra</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
@@ -4120,15 +4087,17 @@
         </is>
       </c>
       <c r="F19" s="7" t="n">
-        <v>0.035</v>
+        <v>10</v>
       </c>
       <c r="G19" s="7" t="n">
-        <v>0.29</v>
+        <v>50</v>
       </c>
       <c r="H19" s="7" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I19" s="7" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>12.5</v>
+      </c>
       <c r="J19" s="7" t="n"/>
       <c r="K19" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F19+Profiles!$B$8*IF(H19="",F19,H19)+Profiles!$B$10*IF(I19="",F19,I19))+Profiles!$C$3*G19)/1000000+Profiles!$D$3*IF(J19="",0,J19)</f>
@@ -4152,55 +4121,51 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
+      <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>openai/gpt-6-astra</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J20" s="7" t="n"/>
-      <c r="K20" s="8">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-max-0902</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F20+Profiles!$B$8*IF(H20="",F20,H20)+Profiles!$B$10*IF(I20="",F20,I20))+Profiles!$C$3*G20)/1000000+Profiles!$D$3*IF(J20="",0,J20)</f>
         <v/>
       </c>
-      <c r="L20" s="8">
+      <c r="L20" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F20+Profiles!$B$8*IF(H20="",F20,H20)+Profiles!$B$10*IF(I20="",F20,I20))+Profiles!$C$4*G20)/1000000+Profiles!$D$4*IF(J20="",0,J20)</f>
         <v/>
       </c>
-      <c r="M20" s="8">
+      <c r="M20" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F20+Profiles!$B$8*IF(H20="",F20,H20)+Profiles!$B$10*IF(I20="",F20,I20))+Profiles!$C$5*G20)/1000000+Profiles!$D$5*IF(J20="",0,J20)</f>
         <v/>
       </c>
-      <c r="N20" s="8">
+      <c r="N20" s="10">
         <f>K20+L20+M20</f>
         <v/>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="10">
         <f>3*N20</f>
         <v/>
       </c>
@@ -4211,28 +4176,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-max-0902</t>
+          <t>meta/muse-spark-1.3-contributor</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cheap contributor tier (check its data terms)</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" s="9" t="n">
-        <v>2</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>6</v>
+        <v>0.2</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I21" s="9" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.002</v>
+      </c>
+      <c r="I21" s="9" t="n"/>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F21+Profiles!$B$8*IF(H21="",F21,H21)+Profiles!$B$10*IF(I21="",F21,I21))+Profiles!$C$3*G21)/1000000+Profiles!$D$3*IF(J21="",0,J21)</f>
@@ -4256,53 +4223,53 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="n">
+      <c r="A22" s="6" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>meta/muse-spark-1.3-contributor</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>meta/muse-spark-1.3</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>cheap contributor tier (check its data terms)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" s="9" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="G22" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H22" s="9" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="10">
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F22+Profiles!$B$8*IF(H22="",F22,H22)+Profiles!$B$10*IF(I22="",F22,I22))+Profiles!$C$3*G22)/1000000+Profiles!$D$3*IF(J22="",0,J22)</f>
         <v/>
       </c>
-      <c r="L22" s="10">
+      <c r="L22" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F22+Profiles!$B$8*IF(H22="",F22,H22)+Profiles!$B$10*IF(I22="",F22,I22))+Profiles!$C$4*G22)/1000000+Profiles!$D$4*IF(J22="",0,J22)</f>
         <v/>
       </c>
-      <c r="M22" s="10">
+      <c r="M22" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F22+Profiles!$B$8*IF(H22="",F22,H22)+Profiles!$B$10*IF(I22="",F22,I22))+Profiles!$C$5*G22)/1000000+Profiles!$D$5*IF(J22="",0,J22)</f>
         <v/>
       </c>
-      <c r="N22" s="10">
+      <c r="N22" s="8">
         <f>K22+L22+M22</f>
         <v/>
       </c>
-      <c r="O22" s="10">
+      <c r="O22" s="8">
         <f>3*N22</f>
         <v/>
       </c>
@@ -4313,7 +4280,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>meta/muse-spark-1.3</t>
+          <t>google/gemini-3.8-flash</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -4328,16 +4295,20 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>4.25</v>
+        <v>3.75</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="7" t="n"/>
+        <v>0.075</v>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="J23" s="7" t="n">
+        <v>7.5e-07</v>
+      </c>
       <c r="K23" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F23+Profiles!$B$8*IF(H23="",F23,H23)+Profiles!$B$10*IF(I23="",F23,I23))+Profiles!$C$3*G23)/1000000+Profiles!$D$3*IF(J23="",0,J23)</f>
         <v/>
@@ -4365,12 +4336,12 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>google/gemini-3.8-flash</t>
+          <t>anthropic/claude-fable-5.1</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr"/>
@@ -4380,20 +4351,18 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.75</v>
+        <v>10</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>3.75</v>
+        <v>50</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>0.075</v>
+        <v>0.25</v>
       </c>
       <c r="I24" s="7" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="J24" s="7" t="n">
-        <v>7.5e-07</v>
-      </c>
+        <v>12.5</v>
+      </c>
+      <c r="J24" s="7" t="n"/>
       <c r="K24" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F24+Profiles!$B$8*IF(H24="",F24,H24)+Profiles!$B$10*IF(I24="",F24,I24))+Profiles!$C$3*G24)/1000000+Profiles!$D$3*IF(J24="",0,J24)</f>
         <v/>
@@ -4416,157 +4385,151 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
+      <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>anthropic/claude-fable-5.1</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.8-flash</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="10">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$3*G25)/1000000+Profiles!$D$3*IF(J25="",0,J25)</f>
+        <v/>
+      </c>
+      <c r="L25" s="10">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$4*G25)/1000000+Profiles!$D$4*IF(J25="",0,J25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="10">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$5*G25)/1000000+Profiles!$D$5*IF(J25="",0,J25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="10">
+        <f>K25+L25+M25</f>
+        <v/>
+      </c>
+      <c r="O25" s="10">
+        <f>3*N25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>z-ai/glm-5.3-flash</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F25" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>50</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="J25" s="7" t="n"/>
-      <c r="K25" s="8">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$3*G25)/1000000+Profiles!$D$3*IF(J25="",0,J25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="8">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$4*G25)/1000000+Profiles!$D$4*IF(J25="",0,J25)</f>
-        <v/>
-      </c>
-      <c r="M25" s="8">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F25+Profiles!$B$8*IF(H25="",F25,H25)+Profiles!$B$10*IF(I25="",F25,I25))+Profiles!$C$5*G25)/1000000+Profiles!$D$5*IF(J25="",0,J25)</f>
-        <v/>
-      </c>
-      <c r="N25" s="8">
-        <f>K25+L25+M25</f>
-        <v/>
-      </c>
-      <c r="O25" s="8">
-        <f>3*N25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>qwen/qwen3.8-flash</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="7" t="n">
         <v>0.15</v>
       </c>
-      <c r="G26" s="9" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H26" s="9" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="I26" s="9" t="n">
+      <c r="G26" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I26" s="7" t="n"/>
+      <c r="J26" s="7" t="n"/>
+      <c r="K26" s="8">
+        <f>(Profiles!$B$3*(Profiles!$B$9*F26+Profiles!$B$8*IF(H26="",F26,H26)+Profiles!$B$10*IF(I26="",F26,I26))+Profiles!$C$3*G26)/1000000+Profiles!$D$3*IF(J26="",0,J26)</f>
+        <v/>
+      </c>
+      <c r="L26" s="8">
+        <f>(Profiles!$B$4*(Profiles!$B$9*F26+Profiles!$B$8*IF(H26="",F26,H26)+Profiles!$B$10*IF(I26="",F26,I26))+Profiles!$C$4*G26)/1000000+Profiles!$D$4*IF(J26="",0,J26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="8">
+        <f>(Profiles!$B$5*(Profiles!$B$9*F26+Profiles!$B$8*IF(H26="",F26,H26)+Profiles!$B$10*IF(I26="",F26,I26))+Profiles!$C$5*G26)/1000000+Profiles!$D$5*IF(J26="",0,J26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="8">
+        <f>K26+L26+M26</f>
+        <v/>
+      </c>
+      <c r="O26" s="8">
+        <f>3*N26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>meta/muse-spark-1.2-contributor</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" s="9" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="G27" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F26+Profiles!$B$8*IF(H26="",F26,H26)+Profiles!$B$10*IF(I26="",F26,I26))+Profiles!$C$3*G26)/1000000+Profiles!$D$3*IF(J26="",0,J26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F26+Profiles!$B$8*IF(H26="",F26,H26)+Profiles!$B$10*IF(I26="",F26,I26))+Profiles!$C$4*G26)/1000000+Profiles!$D$4*IF(J26="",0,J26)</f>
-        <v/>
-      </c>
-      <c r="M26" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F26+Profiles!$B$8*IF(H26="",F26,H26)+Profiles!$B$10*IF(I26="",F26,I26))+Profiles!$C$5*G26)/1000000+Profiles!$D$5*IF(J26="",0,J26)</f>
-        <v/>
-      </c>
-      <c r="N26" s="10">
-        <f>K26+L26+M26</f>
-        <v/>
-      </c>
-      <c r="O26" s="10">
-        <f>3*N26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>z-ai/glm-5.3-flash</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G27" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H27" s="7" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="7" t="n"/>
-      <c r="K27" s="8">
+      <c r="H27" s="9" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n"/>
+      <c r="K27" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F27+Profiles!$B$8*IF(H27="",F27,H27)+Profiles!$B$10*IF(I27="",F27,I27))+Profiles!$C$3*G27)/1000000+Profiles!$D$3*IF(J27="",0,J27)</f>
         <v/>
       </c>
-      <c r="L27" s="8">
+      <c r="L27" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F27+Profiles!$B$8*IF(H27="",F27,H27)+Profiles!$B$10*IF(I27="",F27,I27))+Profiles!$C$4*G27)/1000000+Profiles!$D$4*IF(J27="",0,J27)</f>
         <v/>
       </c>
-      <c r="M27" s="8">
+      <c r="M27" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F27+Profiles!$B$8*IF(H27="",F27,H27)+Profiles!$B$10*IF(I27="",F27,I27))+Profiles!$C$5*G27)/1000000+Profiles!$D$5*IF(J27="",0,J27)</f>
         <v/>
       </c>
-      <c r="N27" s="8">
+      <c r="N27" s="10">
         <f>K27+L27+M27</f>
         <v/>
       </c>
-      <c r="O27" s="8">
+      <c r="O27" s="10">
         <f>3*N27</f>
         <v/>
       </c>
@@ -4577,7 +4540,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>meta/muse-spark-1.2-contributor</t>
+          <t>deepseek/deepseek-v4-flash-vision-exp</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4588,13 +4551,13 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
       <c r="F28" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>0.2</v>
+        <v>1.32</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="I28" s="9" t="n"/>
       <c r="J28" s="9" t="n"/>
@@ -4625,24 +4588,24 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>deepseek/deepseek-v4-flash-vision-exp</t>
+          <t>qwen/qwen3.8-27b</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
       <c r="F29" s="9" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>1.32</v>
+        <v>3</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>0.014</v>
+        <v>0.08499999999999999</v>
       </c>
       <c r="I29" s="9" t="n"/>
       <c r="J29" s="9" t="n"/>
@@ -4673,27 +4636,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>qwen/qwen3.8-27b</t>
+          <t>google/gemini-3.7-flash</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
       <c r="F30" s="9" t="n">
-        <v>0.42</v>
+        <v>0.75</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="H30" s="9" t="n">
-        <v>0.08499999999999999</v>
-      </c>
-      <c r="I30" s="9" t="n"/>
-      <c r="J30" s="9" t="n"/>
+        <v>0.075</v>
+      </c>
+      <c r="I30" s="9" t="n">
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>7.5e-07</v>
+      </c>
       <c r="K30" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F30+Profiles!$B$8*IF(H30="",F30,H30)+Profiles!$B$10*IF(I30="",F30,I30))+Profiles!$C$3*G30)/1000000+Profiles!$D$3*IF(J30="",0,J30)</f>
         <v/>
@@ -4721,31 +4688,25 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>google/gemini-3.7-flash</t>
+          <t>bytedance-seed/seed-2-1-turbo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" s="9" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="G31" s="9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I31" s="9" t="n">
-        <v>0.0416666666666667</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>7.5e-07</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
       <c r="K31" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F31+Profiles!$B$8*IF(H31="",F31,H31)+Profiles!$B$10*IF(I31="",F31,I31))+Profiles!$C$3*G31)/1000000+Profiles!$D$3*IF(J31="",0,J31)</f>
         <v/>
@@ -4773,7 +4734,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bytedance-seed/seed-2-1-turbo</t>
+          <t>bytedance-seed/seed-2.0-code</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4787,7 +4748,7 @@
         <v>0.5</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
@@ -4819,7 +4780,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>bytedance-seed/seed-2.0-code</t>
+          <t>x-ai/grok-4.6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4830,12 +4791,14 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
       <c r="F33" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G33" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="H33" s="9" t="n">
         <v>0.5</v>
       </c>
-      <c r="G33" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
       <c r="J33" s="9" t="n"/>
       <c r="K33" s="10">
@@ -4865,24 +4828,24 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.6</t>
+          <t>meta/muse-glimmer-30b</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" s="9" t="n">
-        <v>2</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>6</v>
+        <v>1.2</v>
       </c>
       <c r="H34" s="9" t="n">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
       <c r="I34" s="9" t="n"/>
       <c r="J34" s="9" t="n"/>
@@ -4913,24 +4876,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>meta/muse-glimmer-30b</t>
+          <t>meta/muse-spark-1.2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
       <c r="F35" s="9" t="n">
-        <v>0.3</v>
+        <v>1.25</v>
       </c>
       <c r="G35" s="9" t="n">
-        <v>1.2</v>
+        <v>4.25</v>
       </c>
       <c r="H35" s="9" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="I35" s="9" t="n"/>
       <c r="J35" s="9" t="n"/>
@@ -4961,24 +4924,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>meta/muse-spark-1.2</t>
+          <t>thinkingmachines/inkling-small</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
       <c r="F36" s="9" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>4.25</v>
+        <v>1.2</v>
       </c>
       <c r="H36" s="9" t="n">
-        <v>0.15</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="I36" s="9" t="n"/>
       <c r="J36" s="9" t="n"/>
@@ -5009,26 +4972,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>thinkingmachines/inkling-small</t>
+          <t>qwen/qwen3.7-flash</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
       <c r="F37" s="9" t="n">
-        <v>0.45</v>
+        <v>0.03</v>
       </c>
       <c r="G37" s="9" t="n">
-        <v>1.2</v>
+        <v>0.13</v>
       </c>
       <c r="H37" s="9" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="I37" s="9" t="n"/>
+        <v>0.006</v>
+      </c>
+      <c r="I37" s="9" t="n">
+        <v>0.03800000000000001</v>
+      </c>
       <c r="J37" s="9" t="n"/>
       <c r="K37" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F37+Profiles!$B$8*IF(H37="",F37,H37)+Profiles!$B$10*IF(I37="",F37,I37))+Profiles!$C$3*G37)/1000000+Profiles!$D$3*IF(J37="",0,J37)</f>
@@ -5057,27 +5022,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-flash</t>
+          <t>anthropic/claude-opus-5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr"/>
       <c r="F38" s="9" t="n">
-        <v>0.03</v>
+        <v>5</v>
       </c>
       <c r="G38" s="9" t="n">
-        <v>0.13</v>
+        <v>25</v>
       </c>
       <c r="H38" s="9" t="n">
-        <v>0.006</v>
+        <v>0.5</v>
       </c>
       <c r="I38" s="9" t="n">
-        <v>0.03800000000000001</v>
+        <v>6.25</v>
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10">
@@ -5107,29 +5072,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>anthropic/claude-opus-5</t>
+          <t>google/gemini-3.6-flash</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr"/>
       <c r="F39" s="9" t="n">
-        <v>5</v>
+        <v>0.75</v>
       </c>
       <c r="G39" s="9" t="n">
-        <v>25</v>
+        <v>3.75</v>
       </c>
       <c r="H39" s="9" t="n">
-        <v>0.5</v>
+        <v>0.075</v>
       </c>
       <c r="I39" s="9" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J39" s="9" t="n"/>
+        <v>0.0416666666666667</v>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>7.5e-07</v>
+      </c>
       <c r="K39" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F39+Profiles!$B$8*IF(H39="",F39,H39)+Profiles!$B$10*IF(I39="",F39,I39))+Profiles!$C$3*G39)/1000000+Profiles!$D$3*IF(J39="",0,J39)</f>
         <v/>
@@ -5157,7 +5124,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>google/gemini-3.6-flash</t>
+          <t>google/gemini-3.5-flash-lite</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5165,22 +5132,26 @@
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Flash Lite line (3.5 is its newest)</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr"/>
       <c r="F40" s="9" t="n">
-        <v>0.75</v>
+        <v>0.3</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>0.075</v>
+        <v>0.03</v>
       </c>
       <c r="I40" s="9" t="n">
-        <v>0.0416666666666667</v>
+        <v>0.0833333333333333</v>
       </c>
       <c r="J40" s="9" t="n">
-        <v>7.5e-07</v>
+        <v>3e-07</v>
       </c>
       <c r="K40" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F40+Profiles!$B$8*IF(H40="",F40,H40)+Profiles!$B$10*IF(I40="",F40,I40))+Profiles!$C$3*G40)/1000000+Profiles!$D$3*IF(J40="",0,J40)</f>
@@ -5209,35 +5180,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>google/gemini-3.5-flash-lite</t>
+          <t>thinkingmachines/inkling</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Flash Lite line (3.5 is its newest)</t>
-        </is>
-      </c>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr"/>
       <c r="F41" s="9" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G41" s="9" t="n">
-        <v>2.5</v>
+        <v>4.05</v>
       </c>
       <c r="H41" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I41" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>3e-07</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="I41" s="9" t="n"/>
+      <c r="J41" s="9" t="n"/>
       <c r="K41" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F41+Profiles!$B$8*IF(H41="",F41,H41)+Profiles!$B$10*IF(I41="",F41,I41))+Profiles!$C$3*G41)/1000000+Profiles!$D$3*IF(J41="",0,J41)</f>
         <v/>
@@ -5260,101 +5223,101 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="n">
+      <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>thinkingmachines/inkling</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>2026-07-17</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="10">
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>moonshotai/kimi-k3</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr"/>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I42" s="7" t="n"/>
+      <c r="J42" s="7" t="n"/>
+      <c r="K42" s="8">
         <f>(Profiles!$B$3*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$3*G42)/1000000+Profiles!$D$3*IF(J42="",0,J42)</f>
         <v/>
       </c>
-      <c r="L42" s="10">
+      <c r="L42" s="8">
         <f>(Profiles!$B$4*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$4*G42)/1000000+Profiles!$D$4*IF(J42="",0,J42)</f>
         <v/>
       </c>
-      <c r="M42" s="10">
+      <c r="M42" s="8">
         <f>(Profiles!$B$5*(Profiles!$B$9*F42+Profiles!$B$8*IF(H42="",F42,H42)+Profiles!$B$10*IF(I42="",F42,I42))+Profiles!$C$5*G42)/1000000+Profiles!$D$5*IF(J42="",0,J42)</f>
         <v/>
       </c>
-      <c r="N42" s="10">
+      <c r="N42" s="8">
         <f>K42+L42+M42</f>
         <v/>
       </c>
-      <c r="O42" s="10">
+      <c r="O42" s="8">
         <f>3*N42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>moonshotai/kimi-k3</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>meta/muse-spark-1.1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr"/>
-      <c r="E43" s="6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G43" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="H43" s="7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I43" s="7" t="n"/>
-      <c r="J43" s="7" t="n"/>
-      <c r="K43" s="8">
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G43" s="9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H43" s="9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I43" s="9" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F43+Profiles!$B$8*IF(H43="",F43,H43)+Profiles!$B$10*IF(I43="",F43,I43))+Profiles!$C$3*G43)/1000000+Profiles!$D$3*IF(J43="",0,J43)</f>
         <v/>
       </c>
-      <c r="L43" s="8">
+      <c r="L43" s="10">
         <f>(Profiles!$B$4*(Profiles!$B$9*F43+Profiles!$B$8*IF(H43="",F43,H43)+Profiles!$B$10*IF(I43="",F43,I43))+Profiles!$C$4*G43)/1000000+Profiles!$D$4*IF(J43="",0,J43)</f>
         <v/>
       </c>
-      <c r="M43" s="8">
+      <c r="M43" s="10">
         <f>(Profiles!$B$5*(Profiles!$B$9*F43+Profiles!$B$8*IF(H43="",F43,H43)+Profiles!$B$10*IF(I43="",F43,I43))+Profiles!$C$5*G43)/1000000+Profiles!$D$5*IF(J43="",0,J43)</f>
         <v/>
       </c>
-      <c r="N43" s="8">
+      <c r="N43" s="10">
         <f>K43+L43+M43</f>
         <v/>
       </c>
-      <c r="O43" s="8">
+      <c r="O43" s="10">
         <f>3*N43</f>
         <v/>
       </c>
@@ -5365,26 +5328,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>meta/muse-spark-1.1</t>
+          <t>openai/gpt-5.6-luna</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
       <c r="F44" s="9" t="n">
-        <v>1.25</v>
+        <v>0.2</v>
       </c>
       <c r="G44" s="9" t="n">
-        <v>4.25</v>
+        <v>1.2</v>
       </c>
       <c r="H44" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I44" s="9" t="n"/>
+        <v>0.02</v>
+      </c>
+      <c r="I44" s="9" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F44+Profiles!$B$8*IF(H44="",F44,H44)+Profiles!$B$10*IF(I44="",F44,I44))+Profiles!$C$3*G44)/1000000+Profiles!$D$3*IF(J44="",0,J44)</f>
@@ -5413,7 +5378,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna</t>
+          <t>openai/gpt-5.6-terra</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5424,16 +5389,16 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
       <c r="F45" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G45" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H45" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G45" s="9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H45" s="9" t="n">
-        <v>0.02</v>
-      </c>
       <c r="I45" s="9" t="n">
-        <v>0.25</v>
+        <v>2.5</v>
       </c>
       <c r="J45" s="9" t="n"/>
       <c r="K45" s="10">
@@ -5463,7 +5428,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-terra</t>
+          <t>openai/gpt-5.6-sol</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5477,7 +5442,7 @@
         <v>2</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H46" s="9" t="n">
         <v>0.2</v>
@@ -5513,12 +5478,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-sol</t>
+          <t>x-ai/grok-4.5</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -5527,14 +5492,12 @@
         <v>2</v>
       </c>
       <c r="G47" s="9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H47" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I47" s="9" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="I47" s="9" t="n"/>
       <c r="J47" s="9" t="n"/>
       <c r="K47" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F47+Profiles!$B$8*IF(H47="",F47,H47)+Profiles!$B$10*IF(I47="",F47,I47))+Profiles!$C$3*G47)/1000000+Profiles!$D$3*IF(J47="",0,J47)</f>
@@ -5563,12 +5526,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.5</t>
+          <t>anthropic/claude-sonnet-5</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -5577,12 +5540,14 @@
         <v>2</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H48" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I48" s="9" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="I48" s="9" t="n">
+        <v>2.5</v>
+      </c>
       <c r="J48" s="9" t="n"/>
       <c r="K48" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F48+Profiles!$B$8*IF(H48="",F48,H48)+Profiles!$B$10*IF(I48="",F48,I48))+Profiles!$C$3*G48)/1000000+Profiles!$D$3*IF(J48="",0,J48)</f>
@@ -5611,28 +5576,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-5</t>
+          <t>moonshotai/kimi-k2.7-code</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" s="9" t="n">
-        <v>2</v>
+        <v>0.6562</v>
       </c>
       <c r="G49" s="9" t="n">
-        <v>10</v>
+        <v>3.3</v>
       </c>
       <c r="H49" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>2.5</v>
-      </c>
+        <v>0.18</v>
+      </c>
+      <c r="I49" s="9" t="n"/>
       <c r="J49" s="9" t="n"/>
       <c r="K49" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F49+Profiles!$B$8*IF(H49="",F49,H49)+Profiles!$B$10*IF(I49="",F49,I49))+Profiles!$C$3*G49)/1000000+Profiles!$D$3*IF(J49="",0,J49)</f>
@@ -5661,26 +5624,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.7-code</t>
+          <t>anthropic/claude-fable-5</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" s="9" t="n">
-        <v>0.6562</v>
+        <v>10</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>3.3</v>
+        <v>50</v>
       </c>
       <c r="H50" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="I50" s="9" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>12.5</v>
+      </c>
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F50+Profiles!$B$8*IF(H50="",F50,H50)+Profiles!$B$10*IF(I50="",F50,I50))+Profiles!$C$3*G50)/1000000+Profiles!$D$3*IF(J50="",0,J50)</f>
@@ -5709,27 +5674,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>anthropic/claude-fable-5</t>
+          <t>qwen/qwen3.7-plus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
       <c r="F51" s="9" t="n">
-        <v>10</v>
+        <v>0.32</v>
       </c>
       <c r="G51" s="9" t="n">
-        <v>50</v>
+        <v>1.28</v>
       </c>
       <c r="H51" s="9" t="n">
-        <v>1</v>
+        <v>0.064</v>
       </c>
       <c r="I51" s="9" t="n">
-        <v>12.5</v>
+        <v>0.4</v>
       </c>
       <c r="J51" s="9" t="n"/>
       <c r="K51" s="10">
@@ -5759,28 +5724,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>qwen/qwen3.7-plus</t>
+          <t>minimax/minimax-m3</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
       <c r="F52" s="9" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="H52" s="9" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="I52" s="9" t="n">
-        <v>0.4</v>
-      </c>
+        <v>0.06</v>
+      </c>
+      <c r="I52" s="9" t="n"/>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F52+Profiles!$B$8*IF(H52="",F52,H52)+Profiles!$B$10*IF(I52="",F52,I52))+Profiles!$C$3*G52)/1000000+Profiles!$D$3*IF(J52="",0,J52)</f>
@@ -5809,24 +5772,24 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>minimax/minimax-m3</t>
+          <t>stepfun/step-3.7-flash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr"/>
       <c r="F53" s="9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G53" s="9" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="H53" s="9" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="9" t="n"/>
       <c r="J53" s="9" t="n"/>
@@ -5857,26 +5820,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>stepfun/step-3.7-flash</t>
+          <t>anthropic/claude-opus-4.8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
       <c r="F54" s="9" t="n">
-        <v>0.2</v>
+        <v>5</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>1.15</v>
+        <v>25</v>
       </c>
       <c r="H54" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I54" s="9" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="I54" s="9" t="n">
+        <v>6.25</v>
+      </c>
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F54+Profiles!$B$8*IF(H54="",F54,H54)+Profiles!$B$10*IF(I54="",F54,I54))+Profiles!$C$3*G54)/1000000+Profiles!$D$3*IF(J54="",0,J54)</f>
@@ -5905,28 +5870,30 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>anthropic/claude-opus-4.8</t>
+          <t>x-ai/grok-build-0.1</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>xAI's coding model</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr"/>
       <c r="F55" s="9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G55" s="9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H55" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I55" s="9" t="n">
-        <v>6.25</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="I55" s="9" t="n"/>
       <c r="J55" s="9" t="n"/>
       <c r="K55" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F55+Profiles!$B$8*IF(H55="",F55,H55)+Profiles!$B$10*IF(I55="",F55,I55))+Profiles!$C$3*G55)/1000000+Profiles!$D$3*IF(J55="",0,J55)</f>
@@ -5955,31 +5922,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>x-ai/grok-build-0.1</t>
+          <t>google/gemini-3.5-flash</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>xAI's coding model</t>
-        </is>
-      </c>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr"/>
       <c r="F56" s="9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H56" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I56" s="9" t="n"/>
-      <c r="J56" s="9" t="n"/>
+        <v>0.15</v>
+      </c>
+      <c r="I56" s="9" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>1.5e-06</v>
+      </c>
       <c r="K56" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F56+Profiles!$B$8*IF(H56="",F56,H56)+Profiles!$B$10*IF(I56="",F56,I56))+Profiles!$C$3*G56)/1000000+Profiles!$D$3*IF(J56="",0,J56)</f>
         <v/>
@@ -6007,30 +5974,30 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>google/gemini-3.5-flash</t>
+          <t>google/gemini-3.1-flash-lite</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G57" s="9" t="n">
         <v>1.5</v>
       </c>
-      <c r="G57" s="9" t="n">
-        <v>9</v>
-      </c>
       <c r="H57" s="9" t="n">
-        <v>0.15</v>
+        <v>0.025</v>
       </c>
       <c r="I57" s="9" t="n">
         <v>0.0833333333333333</v>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.5e-06</v>
+        <v>2.5e-07</v>
       </c>
       <c r="K57" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F57+Profiles!$B$8*IF(H57="",F57,H57)+Profiles!$B$10*IF(I57="",F57,I57))+Profiles!$C$3*G57)/1000000+Profiles!$D$3*IF(J57="",0,J57)</f>
@@ -6059,31 +6026,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>google/gemini-3.1-flash-lite</t>
+          <t>openai/gpt-chat-latest</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" s="9" t="n">
-        <v>0.25</v>
+        <v>5</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>1.5</v>
+        <v>30</v>
       </c>
       <c r="H58" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I58" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J58" s="9" t="n">
-        <v>2.5e-07</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I58" s="9" t="n"/>
+      <c r="J58" s="9" t="n"/>
       <c r="K58" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F58+Profiles!$B$8*IF(H58="",F58,H58)+Profiles!$B$10*IF(I58="",F58,I58))+Profiles!$C$3*G58)/1000000+Profiles!$D$3*IF(J58="",0,J58)</f>
         <v/>
@@ -6111,24 +6074,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>openai/gpt-chat-latest</t>
+          <t>x-ai/grok-4.3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
       <c r="F59" s="9" t="n">
-        <v>5</v>
+        <v>1.25</v>
       </c>
       <c r="G59" s="9" t="n">
-        <v>30</v>
+        <v>2.5</v>
       </c>
       <c r="H59" s="9" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="I59" s="9" t="n"/>
       <c r="J59" s="9" t="n"/>
@@ -6159,24 +6122,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.3</t>
+          <t>mistralai/mistral-medium-3-5</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>cached tokens at 10% per Mistral (not listed on OpenRouter)</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr"/>
       <c r="F60" s="9" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>2.5</v>
+        <v>7.5</v>
       </c>
       <c r="H60" s="9" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="I60" s="9" t="n"/>
       <c r="J60" s="9" t="n"/>
@@ -6207,30 +6174,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3-5</t>
+          <t>qwen/qwen3.5-plus-20260420</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>cached tokens at 10% per Mistral (not listed on OpenRouter)</t>
-        </is>
-      </c>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr"/>
       <c r="F61" s="9" t="n">
-        <v>1.5</v>
+        <v>0.3</v>
       </c>
       <c r="G61" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H61" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I61" s="9" t="n"/>
+        <v>1.8</v>
+      </c>
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n">
+        <v>0.375</v>
+      </c>
       <c r="J61" s="9" t="n"/>
       <c r="K61" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F61+Profiles!$B$8*IF(H61="",F61,H61)+Profiles!$B$10*IF(I61="",F61,I61))+Profiles!$C$3*G61)/1000000+Profiles!$D$3*IF(J61="",0,J61)</f>
@@ -6259,7 +6222,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-plus-20260420</t>
+          <t>qwen/qwen3.6-flash</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6270,14 +6233,14 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" s="9" t="n">
-        <v>0.3</v>
+        <v>0.1875</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>1.8</v>
+        <v>1.125</v>
       </c>
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="n">
-        <v>0.375</v>
+        <v>0.234375</v>
       </c>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="10">
@@ -6307,7 +6270,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-flash</t>
+          <t>qwen/qwen3.6-35b-a3b</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6318,15 +6281,15 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
       <c r="F63" s="9" t="n">
-        <v>0.1875</v>
+        <v>0.15</v>
       </c>
       <c r="G63" s="9" t="n">
-        <v>1.125</v>
-      </c>
-      <c r="H63" s="9" t="n"/>
-      <c r="I63" s="9" t="n">
-        <v>0.234375</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H63" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I63" s="9" t="n"/>
       <c r="J63" s="9" t="n"/>
       <c r="K63" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F63+Profiles!$B$8*IF(H63="",F63,H63)+Profiles!$B$10*IF(I63="",F63,I63))+Profiles!$C$3*G63)/1000000+Profiles!$D$3*IF(J63="",0,J63)</f>
@@ -6355,7 +6318,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-35b-a3b</t>
+          <t>qwen/qwen3.6-27b</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6366,14 +6329,12 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr"/>
       <c r="F64" s="9" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="G64" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="9" t="n">
-        <v>0.05</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="H64" s="9" t="n"/>
       <c r="I64" s="9" t="n"/>
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="10">
@@ -6403,23 +6364,25 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-27b</t>
+          <t>openai/gpt-5.5</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr"/>
       <c r="F65" s="9" t="n">
-        <v>0.32</v>
+        <v>5</v>
       </c>
       <c r="G65" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H65" s="9" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="H65" s="9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I65" s="9" t="n"/>
       <c r="J65" s="9" t="n"/>
       <c r="K65" s="10">
@@ -6449,24 +6412,24 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5</t>
+          <t>xiaomi/mimo-v2.5</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr"/>
       <c r="F66" s="9" t="n">
-        <v>5</v>
+        <v>0.14</v>
       </c>
       <c r="G66" s="9" t="n">
-        <v>30</v>
+        <v>0.28</v>
       </c>
       <c r="H66" s="9" t="n">
-        <v>0.5</v>
+        <v>0.0028</v>
       </c>
       <c r="I66" s="9" t="n"/>
       <c r="J66" s="9" t="n"/>
@@ -6497,24 +6460,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>xiaomi/mimo-v2.5</t>
+          <t>moonshotai/kimi-k2.6</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" s="9" t="n">
-        <v>0.14</v>
+        <v>0.65</v>
       </c>
       <c r="G67" s="9" t="n">
-        <v>0.28</v>
+        <v>3.41</v>
       </c>
       <c r="H67" s="9" t="n">
-        <v>0.0028</v>
+        <v>0.15</v>
       </c>
       <c r="I67" s="9" t="n"/>
       <c r="J67" s="9" t="n"/>
@@ -6545,26 +6508,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.6</t>
+          <t>anthropic/claude-opus-4.7</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" s="9" t="n">
-        <v>0.65</v>
+        <v>5</v>
       </c>
       <c r="G68" s="9" t="n">
-        <v>3.41</v>
+        <v>25</v>
       </c>
       <c r="H68" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I68" s="9" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="I68" s="9" t="n">
+        <v>6.25</v>
+      </c>
       <c r="J68" s="9" t="n"/>
       <c r="K68" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F68+Profiles!$B$8*IF(H68="",F68,H68)+Profiles!$B$10*IF(I68="",F68,I68))+Profiles!$C$3*G68)/1000000+Profiles!$D$3*IF(J68="",0,J68)</f>
@@ -6593,28 +6558,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>anthropic/claude-opus-4.7</t>
+          <t>google/gemma-4-26b-a4b-it</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr"/>
       <c r="F69" s="9" t="n">
-        <v>5</v>
+        <v>0.09</v>
       </c>
       <c r="G69" s="9" t="n">
-        <v>25</v>
+        <v>0.3</v>
       </c>
       <c r="H69" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I69" s="9" t="n">
-        <v>6.25</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I69" s="9" t="n"/>
       <c r="J69" s="9" t="n"/>
       <c r="K69" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F69+Profiles!$B$8*IF(H69="",F69,H69)+Profiles!$B$10*IF(I69="",F69,I69))+Profiles!$C$3*G69)/1000000+Profiles!$D$3*IF(J69="",0,J69)</f>
@@ -6643,12 +6606,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>google/gemma-4-26b-a4b-it</t>
+          <t>google/gemma-4-31b-it</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -6657,7 +6620,7 @@
         <v>0.09</v>
       </c>
       <c r="G70" s="9" t="n">
-        <v>0.3</v>
+        <v>0.34</v>
       </c>
       <c r="H70" s="9" t="n">
         <v>0.05</v>
@@ -6691,7 +6654,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>google/gemma-4-31b-it</t>
+          <t>qwen/qwen3.6-plus</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -6702,15 +6665,15 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr"/>
       <c r="F71" s="9" t="n">
-        <v>0.09</v>
+        <v>0.325</v>
       </c>
       <c r="G71" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H71" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I71" s="9" t="n"/>
+        <v>1.95</v>
+      </c>
+      <c r="H71" s="9" t="n"/>
+      <c r="I71" s="9" t="n">
+        <v>0.40625</v>
+      </c>
       <c r="J71" s="9" t="n"/>
       <c r="K71" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F71+Profiles!$B$8*IF(H71="",F71,H71)+Profiles!$B$10*IF(I71="",F71,I71))+Profiles!$C$3*G71)/1000000+Profiles!$D$3*IF(J71="",0,J71)</f>
@@ -6739,26 +6702,26 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>qwen/qwen3.6-plus</t>
+          <t>z-ai/glm-5v-turbo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr"/>
       <c r="F72" s="9" t="n">
-        <v>0.325</v>
+        <v>1.2</v>
       </c>
       <c r="G72" s="9" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H72" s="9" t="n"/>
-      <c r="I72" s="9" t="n">
-        <v>0.40625</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H72" s="9" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I72" s="9" t="n"/>
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F72+Profiles!$B$8*IF(H72="",F72,H72)+Profiles!$B$10*IF(I72="",F72,I72))+Profiles!$C$3*G72)/1000000+Profiles!$D$3*IF(J72="",0,J72)</f>
@@ -6787,24 +6750,24 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>z-ai/glm-5v-turbo</t>
+          <t>x-ai/grok-4.20</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr"/>
       <c r="F73" s="9" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="G73" s="9" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="H73" s="9" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="I73" s="9" t="n"/>
       <c r="J73" s="9" t="n"/>
@@ -6835,24 +6798,24 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>x-ai/grok-4.20</t>
+          <t>openai/gpt-5.4-nano</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr"/>
       <c r="F74" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G74" s="9" t="n">
         <v>1.25</v>
       </c>
-      <c r="G74" s="9" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H74" s="9" t="n">
-        <v>0.2</v>
+        <v>0.02</v>
       </c>
       <c r="I74" s="9" t="n"/>
       <c r="J74" s="9" t="n"/>
@@ -6883,23 +6846,25 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>rekaai/reka-edge</t>
+          <t>openai/gpt-5.4-mini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr"/>
       <c r="F75" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.75</v>
       </c>
       <c r="G75" s="9" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="H75" s="9" t="n"/>
+        <v>4.5</v>
+      </c>
+      <c r="H75" s="9" t="n">
+        <v>0.075</v>
+      </c>
       <c r="I75" s="9" t="n"/>
       <c r="J75" s="9" t="n"/>
       <c r="K75" s="10">
@@ -6929,24 +6894,24 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-nano</t>
+          <t>mistralai/mistral-small-2603</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr"/>
       <c r="F76" s="9" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="G76" s="9" t="n">
-        <v>1.25</v>
+        <v>0.6</v>
       </c>
       <c r="H76" s="9" t="n">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="I76" s="9" t="n"/>
       <c r="J76" s="9" t="n"/>
@@ -6977,25 +6942,23 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-mini</t>
+          <t>bytedance-seed/seed-2.0-lite</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr"/>
       <c r="F77" s="9" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="G77" s="9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H77" s="9" t="n">
-        <v>0.075</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H77" s="9" t="n"/>
       <c r="I77" s="9" t="n"/>
       <c r="J77" s="9" t="n"/>
       <c r="K77" s="10">
@@ -7025,25 +6988,23 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-2603</t>
+          <t>qwen/qwen3.5-9b</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr"/>
       <c r="F78" s="9" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="G78" s="9" t="n">
         <v>0.15</v>
       </c>
-      <c r="G78" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H78" s="9" t="n">
-        <v>0.015</v>
-      </c>
+      <c r="H78" s="9" t="n"/>
       <c r="I78" s="9" t="n"/>
       <c r="J78" s="9" t="n"/>
       <c r="K78" s="10">
@@ -7073,23 +7034,25 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>bytedance-seed/seed-2.0-lite</t>
+          <t>openai/gpt-5.4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr"/>
       <c r="F79" s="9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G79" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H79" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="G79" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H79" s="9" t="n"/>
       <c r="I79" s="9" t="n"/>
       <c r="J79" s="9" t="n"/>
       <c r="K79" s="10">
@@ -7119,12 +7082,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-9b</t>
+          <t>bytedance-seed/seed-2.0-mini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
@@ -7133,7 +7096,7 @@
         <v>0.09999999999999999</v>
       </c>
       <c r="G80" s="9" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="9" t="n"/>
@@ -7165,25 +7128,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4</t>
+          <t>qwen/qwen3.5-35b-a3b</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr"/>
       <c r="F81" s="9" t="n">
-        <v>2.5</v>
+        <v>0.1625</v>
       </c>
       <c r="G81" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H81" s="9" t="n">
-        <v>0.25</v>
-      </c>
+        <v>1.3</v>
+      </c>
+      <c r="H81" s="9" t="n"/>
       <c r="I81" s="9" t="n"/>
       <c r="J81" s="9" t="n"/>
       <c r="K81" s="10">
@@ -7213,31 +7174,25 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>google/gemini-3.1-flash-lite-preview</t>
+          <t>qwen/qwen3.5-27b</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr"/>
       <c r="F82" s="9" t="n">
-        <v>0.25</v>
+        <v>0.195</v>
       </c>
       <c r="G82" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H82" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I82" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J82" s="9" t="n">
-        <v>2.5e-07</v>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="H82" s="9" t="n"/>
+      <c r="I82" s="9" t="n"/>
+      <c r="J82" s="9" t="n"/>
       <c r="K82" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F82+Profiles!$B$8*IF(H82="",F82,H82)+Profiles!$B$10*IF(I82="",F82,I82))+Profiles!$C$3*G82)/1000000+Profiles!$D$3*IF(J82="",0,J82)</f>
         <v/>
@@ -7265,21 +7220,21 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>bytedance-seed/seed-2.0-mini</t>
+          <t>qwen/qwen3.5-122b-a10b</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
       <c r="F83" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="G83" s="9" t="n">
-        <v>0.4</v>
+        <v>2.08</v>
       </c>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="9" t="n"/>
@@ -7311,7 +7266,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-35b-a3b</t>
+          <t>qwen/qwen3.5-flash-02-23</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7322,10 +7277,10 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr"/>
       <c r="F84" s="9" t="n">
-        <v>0.1625</v>
+        <v>0.065</v>
       </c>
       <c r="G84" s="9" t="n">
-        <v>1.3</v>
+        <v>0.26</v>
       </c>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="n"/>
@@ -7357,23 +7312,25 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-27b</t>
+          <t>openai/gpt-5.3-codex</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr"/>
       <c r="F85" s="9" t="n">
-        <v>0.195</v>
+        <v>1.75</v>
       </c>
       <c r="G85" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H85" s="9" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="H85" s="9" t="n">
+        <v>0.175</v>
+      </c>
       <c r="I85" s="9" t="n"/>
       <c r="J85" s="9" t="n"/>
       <c r="K85" s="10">
@@ -7403,25 +7360,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-122b-a10b</t>
+          <t>google/gemini-3.1-pro-preview</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr"/>
       <c r="F86" s="9" t="n">
-        <v>0.26</v>
+        <v>2</v>
       </c>
       <c r="G86" s="9" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="H86" s="9" t="n"/>
-      <c r="I86" s="9" t="n"/>
-      <c r="J86" s="9" t="n"/>
+        <v>12</v>
+      </c>
+      <c r="H86" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I86" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>2e-06</v>
+      </c>
       <c r="K86" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F86+Profiles!$B$8*IF(H86="",F86,H86)+Profiles!$B$10*IF(I86="",F86,I86))+Profiles!$C$3*G86)/1000000+Profiles!$D$3*IF(J86="",0,J86)</f>
         <v/>
@@ -7449,24 +7412,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-flash-02-23</t>
+          <t>anthropic/claude-sonnet-4.6</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr"/>
       <c r="F87" s="9" t="n">
-        <v>0.065</v>
+        <v>3</v>
       </c>
       <c r="G87" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="H87" s="9" t="n"/>
-      <c r="I87" s="9" t="n"/>
+        <v>15</v>
+      </c>
+      <c r="H87" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I87" s="9" t="n">
+        <v>3.75</v>
+      </c>
       <c r="J87" s="9" t="n"/>
       <c r="K87" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F87+Profiles!$B$8*IF(H87="",F87,H87)+Profiles!$B$10*IF(I87="",F87,I87))+Profiles!$C$3*G87)/1000000+Profiles!$D$3*IF(J87="",0,J87)</f>
@@ -7495,31 +7462,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>google/gemini-3.1-pro-preview-customtools</t>
+          <t>qwen/qwen3.5-397b-a17b</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr"/>
       <c r="F88" s="9" t="n">
-        <v>2</v>
+        <v>0.55</v>
       </c>
       <c r="G88" s="9" t="n">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="H88" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I88" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J88" s="9" t="n">
-        <v>2e-06</v>
-      </c>
+        <v>0.225</v>
+      </c>
+      <c r="I88" s="9" t="n"/>
+      <c r="J88" s="9" t="n"/>
       <c r="K88" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F88+Profiles!$B$8*IF(H88="",F88,H88)+Profiles!$B$10*IF(I88="",F88,I88))+Profiles!$C$3*G88)/1000000+Profiles!$D$3*IF(J88="",0,J88)</f>
         <v/>
@@ -7547,26 +7510,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>openai/gpt-5.3-codex</t>
+          <t>anthropic/claude-opus-4.6</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
       <c r="F89" s="9" t="n">
-        <v>1.75</v>
+        <v>5</v>
       </c>
       <c r="G89" s="9" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H89" s="9" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="I89" s="9" t="n"/>
+        <v>0.5</v>
+      </c>
+      <c r="I89" s="9" t="n">
+        <v>6.25</v>
+      </c>
       <c r="J89" s="9" t="n"/>
       <c r="K89" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F89+Profiles!$B$8*IF(H89="",F89,H89)+Profiles!$B$10*IF(I89="",F89,I89))+Profiles!$C$3*G89)/1000000+Profiles!$D$3*IF(J89="",0,J89)</f>
@@ -7595,31 +7560,25 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>google/gemini-3.1-pro-preview</t>
+          <t>openrouter/free</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G90" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="H90" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I90" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J90" s="9" t="n">
-        <v>2e-06</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H90" s="9" t="n"/>
+      <c r="I90" s="9" t="n"/>
+      <c r="J90" s="9" t="n"/>
       <c r="K90" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F90+Profiles!$B$8*IF(H90="",F90,H90)+Profiles!$B$10*IF(I90="",F90,I90))+Profiles!$C$3*G90)/1000000+Profiles!$D$3*IF(J90="",0,J90)</f>
         <v/>
@@ -7647,28 +7606,26 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-4.6</t>
+          <t>moonshotai/kimi-k2.5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr"/>
       <c r="F91" s="9" t="n">
-        <v>3</v>
+        <v>0.45</v>
       </c>
       <c r="G91" s="9" t="n">
-        <v>15</v>
+        <v>2.25</v>
       </c>
       <c r="H91" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I91" s="9" t="n">
-        <v>3.75</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I91" s="9" t="n"/>
       <c r="J91" s="9" t="n"/>
       <c r="K91" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F91+Profiles!$B$8*IF(H91="",F91,H91)+Profiles!$B$10*IF(I91="",F91,I91))+Profiles!$C$3*G91)/1000000+Profiles!$D$3*IF(J91="",0,J91)</f>
@@ -7697,23 +7654,25 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-plus-02-15</t>
+          <t>openai/gpt-5.2-codex</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr"/>
       <c r="F92" s="9" t="n">
-        <v>0.26</v>
+        <v>1.75</v>
       </c>
       <c r="G92" s="9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="H92" s="9" t="n"/>
+        <v>14</v>
+      </c>
+      <c r="H92" s="9" t="n">
+        <v>0.175</v>
+      </c>
       <c r="I92" s="9" t="n"/>
       <c r="J92" s="9" t="n"/>
       <c r="K92" s="10">
@@ -7743,25 +7702,23 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>qwen/qwen3.5-397b-a17b</t>
+          <t>bytedance-seed/seed-1.6-flash</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr"/>
       <c r="F93" s="9" t="n">
-        <v>0.55</v>
+        <v>0.075</v>
       </c>
       <c r="G93" s="9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="H93" s="9" t="n">
-        <v>0.225</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="H93" s="9" t="n"/>
       <c r="I93" s="9" t="n"/>
       <c r="J93" s="9" t="n"/>
       <c r="K93" s="10">
@@ -7791,28 +7748,24 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>anthropic/claude-opus-4.6</t>
+          <t>bytedance-seed/seed-1.6</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
       <c r="F94" s="9" t="n">
-        <v>5</v>
+        <v>0.25</v>
       </c>
       <c r="G94" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H94" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I94" s="9" t="n">
-        <v>6.25</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="9" t="n"/>
       <c r="J94" s="9" t="n"/>
       <c r="K94" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F94+Profiles!$B$8*IF(H94="",F94,H94)+Profiles!$B$10*IF(I94="",F94,I94))+Profiles!$C$3*G94)/1000000+Profiles!$D$3*IF(J94="",0,J94)</f>
@@ -7841,25 +7794,31 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>openrouter/free</t>
+          <t>google/gemini-3-flash-preview</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
       <c r="F95" s="9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G95" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H95" s="9" t="n"/>
-      <c r="I95" s="9" t="n"/>
-      <c r="J95" s="9" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H95" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I95" s="9" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>5e-07</v>
+      </c>
       <c r="K95" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F95+Profiles!$B$8*IF(H95="",F95,H95)+Profiles!$B$10*IF(I95="",F95,I95))+Profiles!$C$3*G95)/1000000+Profiles!$D$3*IF(J95="",0,J95)</f>
         <v/>
@@ -7887,24 +7846,24 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>moonshotai/kimi-k2.5</t>
+          <t>openai/gpt-5.2-chat</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr"/>
       <c r="F96" s="9" t="n">
-        <v>0.45</v>
+        <v>1.75</v>
       </c>
       <c r="G96" s="9" t="n">
-        <v>2.25</v>
+        <v>14</v>
       </c>
       <c r="H96" s="9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.175</v>
       </c>
       <c r="I96" s="9" t="n"/>
       <c r="J96" s="9" t="n"/>
@@ -7935,12 +7894,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-codex</t>
+          <t>openai/gpt-5.2</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -7983,23 +7942,25 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>bytedance-seed/seed-1.6-flash</t>
+          <t>z-ai/glm-4.6v</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr"/>
       <c r="F98" s="9" t="n">
-        <v>0.075</v>
+        <v>0.3</v>
       </c>
       <c r="G98" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H98" s="9" t="n"/>
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="H98" s="9" t="n">
+        <v>0.055</v>
+      </c>
       <c r="I98" s="9" t="n"/>
       <c r="J98" s="9" t="n"/>
       <c r="K98" s="10">
@@ -8029,23 +7990,25 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>bytedance-seed/seed-1.6</t>
+          <t>openai/gpt-5.1-codex-max</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr"/>
       <c r="F99" s="9" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="G99" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H99" s="9" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="H99" s="9" t="n">
+        <v>0.125</v>
+      </c>
       <c r="I99" s="9" t="n"/>
       <c r="J99" s="9" t="n"/>
       <c r="K99" s="10">
@@ -8075,31 +8038,25 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>google/gemini-3-flash-preview</t>
+          <t>amazon/nova-2-lite-v1</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr"/>
       <c r="F100" s="9" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="G100" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H100" s="9" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I100" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J100" s="9" t="n">
-        <v>5e-07</v>
-      </c>
+        <v>2.5</v>
+      </c>
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="9" t="n"/>
+      <c r="J100" s="9" t="n"/>
       <c r="K100" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F100+Profiles!$B$8*IF(H100="",F100,H100)+Profiles!$B$10*IF(I100="",F100,I100))+Profiles!$C$3*G100)/1000000+Profiles!$D$3*IF(J100="",0,J100)</f>
         <v/>
@@ -8127,24 +8084,24 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-chat</t>
+          <t>mistralai/ministral-14b-2512</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr"/>
       <c r="F101" s="9" t="n">
-        <v>1.75</v>
+        <v>0.2</v>
       </c>
       <c r="G101" s="9" t="n">
-        <v>14</v>
+        <v>0.2</v>
       </c>
       <c r="H101" s="9" t="n">
-        <v>0.175</v>
+        <v>0.02</v>
       </c>
       <c r="I101" s="9" t="n"/>
       <c r="J101" s="9" t="n"/>
@@ -8175,24 +8132,24 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2</t>
+          <t>mistralai/ministral-8b-2512</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr"/>
       <c r="F102" s="9" t="n">
-        <v>1.75</v>
+        <v>0.15</v>
       </c>
       <c r="G102" s="9" t="n">
-        <v>14</v>
+        <v>0.15</v>
       </c>
       <c r="H102" s="9" t="n">
-        <v>0.175</v>
+        <v>0.015</v>
       </c>
       <c r="I102" s="9" t="n"/>
       <c r="J102" s="9" t="n"/>
@@ -8223,24 +8180,24 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.6v</t>
+          <t>mistralai/ministral-3b-2512</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
       <c r="F103" s="9" t="n">
-        <v>0.3</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="G103" s="9" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="H103" s="9" t="n">
-        <v>0.055</v>
+        <v>0.01</v>
       </c>
       <c r="I103" s="9" t="n"/>
       <c r="J103" s="9" t="n"/>
@@ -8271,24 +8228,24 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1-codex-max</t>
+          <t>mistralai/mistral-large-2512</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
       <c r="F104" s="9" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="G104" s="9" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="H104" s="9" t="n">
-        <v>0.125</v>
+        <v>0.05</v>
       </c>
       <c r="I104" s="9" t="n"/>
       <c r="J104" s="9" t="n"/>
@@ -8319,24 +8276,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>amazon/nova-2-lite-v1</t>
+          <t>anthropic/claude-opus-4.5</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" s="9" t="n">
-        <v>0.3</v>
+        <v>5</v>
       </c>
       <c r="G105" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H105" s="9" t="n"/>
-      <c r="I105" s="9" t="n"/>
+        <v>25</v>
+      </c>
+      <c r="H105" s="9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I105" s="9" t="n">
+        <v>6.25</v>
+      </c>
       <c r="J105" s="9" t="n"/>
       <c r="K105" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F105+Profiles!$B$8*IF(H105="",F105,H105)+Profiles!$B$10*IF(I105="",F105,I105))+Profiles!$C$3*G105)/1000000+Profiles!$D$3*IF(J105="",0,J105)</f>
@@ -8365,24 +8326,24 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>mistralai/ministral-14b-2512</t>
+          <t>openai/gpt-5.1</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr"/>
       <c r="F106" s="9" t="n">
-        <v>0.2</v>
+        <v>1.25</v>
       </c>
       <c r="G106" s="9" t="n">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="H106" s="9" t="n">
-        <v>0.02</v>
+        <v>0.125</v>
       </c>
       <c r="I106" s="9" t="n"/>
       <c r="J106" s="9" t="n"/>
@@ -8413,24 +8374,24 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>mistralai/ministral-8b-2512</t>
+          <t>openai/gpt-5.1-codex</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
       <c r="F107" s="9" t="n">
-        <v>0.15</v>
+        <v>1.25</v>
       </c>
       <c r="G107" s="9" t="n">
-        <v>0.15</v>
+        <v>10</v>
       </c>
       <c r="H107" s="9" t="n">
-        <v>0.015</v>
+        <v>0.13</v>
       </c>
       <c r="I107" s="9" t="n"/>
       <c r="J107" s="9" t="n"/>
@@ -8461,24 +8422,24 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>mistralai/ministral-3b-2512</t>
+          <t>openai/gpt-5.1-codex-mini</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
       <c r="F108" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.25</v>
       </c>
       <c r="G108" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>2</v>
       </c>
       <c r="H108" s="9" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I108" s="9" t="n"/>
       <c r="J108" s="9" t="n"/>
@@ -8509,24 +8470,24 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>mistralai/mistral-large-2512</t>
+          <t>amazon/nova-premier-v1</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr"/>
       <c r="F109" s="9" t="n">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="G109" s="9" t="n">
-        <v>1.5</v>
+        <v>12.5</v>
       </c>
       <c r="H109" s="9" t="n">
-        <v>0.05</v>
+        <v>0.625</v>
       </c>
       <c r="I109" s="9" t="n"/>
       <c r="J109" s="9" t="n"/>
@@ -8557,28 +8518,24 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>anthropic/claude-opus-4.5</t>
+          <t>qwen/qwen3-vl-32b-instruct</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr"/>
       <c r="F110" s="9" t="n">
-        <v>5</v>
+        <v>0.104</v>
       </c>
       <c r="G110" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="H110" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="I110" s="9" t="n">
-        <v>6.25</v>
-      </c>
+        <v>0.416</v>
+      </c>
+      <c r="H110" s="9" t="n"/>
+      <c r="I110" s="9" t="n"/>
       <c r="J110" s="9" t="n"/>
       <c r="K110" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F110+Profiles!$B$8*IF(H110="",F110,H110)+Profiles!$B$10*IF(I110="",F110,I110))+Profiles!$C$3*G110)/1000000+Profiles!$D$3*IF(J110="",0,J110)</f>
@@ -8607,26 +8564,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1</t>
+          <t>anthropic/claude-haiku-4.5</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="H111" s="9" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="I111" s="9" t="n">
         <v>1.25</v>
       </c>
-      <c r="G111" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H111" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I111" s="9" t="n"/>
       <c r="J111" s="9" t="n"/>
       <c r="K111" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F111+Profiles!$B$8*IF(H111="",F111,H111)+Profiles!$B$10*IF(I111="",F111,I111))+Profiles!$C$3*G111)/1000000+Profiles!$D$3*IF(J111="",0,J111)</f>
@@ -8655,25 +8614,23 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1-codex</t>
+          <t>qwen/qwen3-vl-8b-thinking</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr"/>
       <c r="F112" s="9" t="n">
-        <v>1.25</v>
+        <v>0.18</v>
       </c>
       <c r="G112" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H112" s="9" t="n">
-        <v>0.13</v>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="H112" s="9" t="n"/>
       <c r="I112" s="9" t="n"/>
       <c r="J112" s="9" t="n"/>
       <c r="K112" s="10">
@@ -8703,25 +8660,23 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>openai/gpt-5.1-codex-mini</t>
+          <t>qwen/qwen3-vl-8b-instruct</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr"/>
       <c r="F113" s="9" t="n">
-        <v>0.25</v>
+        <v>0.117</v>
       </c>
       <c r="G113" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H113" s="9" t="n">
-        <v>0.03</v>
-      </c>
+        <v>0.455</v>
+      </c>
+      <c r="H113" s="9" t="n"/>
       <c r="I113" s="9" t="n"/>
       <c r="J113" s="9" t="n"/>
       <c r="K113" s="10">
@@ -8751,25 +8706,23 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>amazon/nova-premier-v1</t>
+          <t>qwen/qwen3-vl-30b-a3b-thinking</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr"/>
       <c r="F114" s="9" t="n">
-        <v>2.5</v>
+        <v>0.2</v>
       </c>
       <c r="G114" s="9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="H114" s="9" t="n">
-        <v>0.625</v>
-      </c>
+        <v>2.4</v>
+      </c>
+      <c r="H114" s="9" t="n"/>
       <c r="I114" s="9" t="n"/>
       <c r="J114" s="9" t="n"/>
       <c r="K114" s="10">
@@ -8799,21 +8752,21 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-32b-instruct</t>
+          <t>qwen/qwen3-vl-30b-a3b-instruct</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
       <c r="F115" s="9" t="n">
-        <v>0.104</v>
+        <v>0.15</v>
       </c>
       <c r="G115" s="9" t="n">
-        <v>0.416</v>
+        <v>0.6</v>
       </c>
       <c r="H115" s="9" t="n"/>
       <c r="I115" s="9" t="n"/>
@@ -8845,27 +8798,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>anthropic/claude-haiku-4.5</t>
+          <t>anthropic/claude-sonnet-4.5</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr"/>
       <c r="F116" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G116" s="9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H116" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="I116" s="9" t="n">
-        <v>1.25</v>
+        <v>3.75</v>
       </c>
       <c r="J116" s="9" t="n"/>
       <c r="K116" s="10">
@@ -8895,21 +8848,21 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-8b-thinking</t>
+          <t>qwen/qwen3-vl-235b-a22b-thinking</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr"/>
       <c r="F117" s="9" t="n">
-        <v>0.18</v>
+        <v>0.4</v>
       </c>
       <c r="G117" s="9" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="H117" s="9" t="n"/>
       <c r="I117" s="9" t="n"/>
@@ -8941,23 +8894,25 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-8b-instruct</t>
+          <t>qwen/qwen3-vl-235b-a22b-instruct</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-09-24</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr"/>
       <c r="F118" s="9" t="n">
-        <v>0.117</v>
+        <v>0.21</v>
       </c>
       <c r="G118" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="H118" s="9" t="n"/>
+        <v>1.9</v>
+      </c>
+      <c r="H118" s="9" t="n">
+        <v>0.09999999999999999</v>
+      </c>
       <c r="I118" s="9" t="n"/>
       <c r="J118" s="9" t="n"/>
       <c r="K118" s="10">
@@ -8987,23 +8942,25 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-30b-a3b-thinking</t>
+          <t>mistralai/mistral-medium-3.1</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
       <c r="F119" s="9" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="G119" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H119" s="9" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H119" s="9" t="n">
+        <v>0.04</v>
+      </c>
       <c r="I119" s="9" t="n"/>
       <c r="J119" s="9" t="n"/>
       <c r="K119" s="10">
@@ -9033,23 +8990,25 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-30b-a3b-instruct</t>
+          <t>openai/gpt-5</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
       <c r="F120" s="9" t="n">
-        <v>0.15</v>
+        <v>1.25</v>
       </c>
       <c r="G120" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H120" s="9" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="H120" s="9" t="n">
+        <v>0.125</v>
+      </c>
       <c r="I120" s="9" t="n"/>
       <c r="J120" s="9" t="n"/>
       <c r="K120" s="10">
@@ -9079,28 +9038,26 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-4.5</t>
+          <t>openai/gpt-5-mini</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
       <c r="F121" s="9" t="n">
-        <v>3</v>
+        <v>0.25</v>
       </c>
       <c r="G121" s="9" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H121" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I121" s="9" t="n">
-        <v>3.75</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="I121" s="9" t="n"/>
       <c r="J121" s="9" t="n"/>
       <c r="K121" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F121+Profiles!$B$8*IF(H121="",F121,H121)+Profiles!$B$10*IF(I121="",F121,I121))+Profiles!$C$3*G121)/1000000+Profiles!$D$3*IF(J121="",0,J121)</f>
@@ -9129,23 +9086,25 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-235b-a22b-thinking</t>
+          <t>openai/gpt-5-nano</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-08-07</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr"/>
       <c r="F122" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G122" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G122" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="H122" s="9" t="n"/>
+      <c r="H122" s="9" t="n">
+        <v>0.005</v>
+      </c>
       <c r="I122" s="9" t="n"/>
       <c r="J122" s="9" t="n"/>
       <c r="K122" s="10">
@@ -9175,26 +9134,32 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>qwen/qwen3-vl-235b-a22b-instruct</t>
+          <t>anthropic/claude-opus-4.1</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>historical Opus (old pricing)</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr"/>
       <c r="F123" s="9" t="n">
-        <v>0.21</v>
+        <v>15</v>
       </c>
       <c r="G123" s="9" t="n">
-        <v>1.9</v>
+        <v>75</v>
       </c>
       <c r="H123" s="9" t="n">
-        <v>0.09999999999999999</v>
-      </c>
-      <c r="I123" s="9" t="n"/>
+        <v>1.5</v>
+      </c>
+      <c r="I123" s="9" t="n">
+        <v>18.75</v>
+      </c>
       <c r="J123" s="9" t="n"/>
       <c r="K123" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F123+Profiles!$B$8*IF(H123="",F123,H123)+Profiles!$B$10*IF(I123="",F123,I123))+Profiles!$C$3*G123)/1000000+Profiles!$D$3*IF(J123="",0,J123)</f>
@@ -9223,27 +9188,31 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3.1</t>
+          <t>google/gemini-2.5-flash-lite</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr"/>
       <c r="F124" s="9" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="G124" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="G124" s="9" t="n">
-        <v>2</v>
-      </c>
       <c r="H124" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I124" s="9" t="n"/>
-      <c r="J124" s="9" t="n"/>
+        <v>0.01</v>
+      </c>
+      <c r="I124" s="9" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>1e-07</v>
+      </c>
       <c r="K124" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F124+Profiles!$B$8*IF(H124="",F124,H124)+Profiles!$B$10*IF(I124="",F124,I124))+Profiles!$C$3*G124)/1000000+Profiles!$D$3*IF(J124="",0,J124)</f>
         <v/>
@@ -9271,25 +9240,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>z-ai/glm-4.5v</t>
+          <t>mistralai/mistral-small-3.2-24b-instruct</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr"/>
       <c r="F125" s="9" t="n">
-        <v>0.6</v>
+        <v>0.09375</v>
       </c>
       <c r="G125" s="9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H125" s="9" t="n">
-        <v>0.11</v>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="H125" s="9" t="n"/>
       <c r="I125" s="9" t="n"/>
       <c r="J125" s="9" t="n"/>
       <c r="K125" s="10">
@@ -9319,27 +9286,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>openai/gpt-5</t>
+          <t>google/gemini-2.5-flash</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr"/>
       <c r="F126" s="9" t="n">
-        <v>1.25</v>
+        <v>0.3</v>
       </c>
       <c r="G126" s="9" t="n">
-        <v>10</v>
+        <v>2.5</v>
       </c>
       <c r="H126" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I126" s="9" t="n"/>
-      <c r="J126" s="9" t="n"/>
+        <v>0.03</v>
+      </c>
+      <c r="I126" s="9" t="n">
+        <v>0.0833333333333333</v>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>3e-07</v>
+      </c>
       <c r="K126" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F126+Profiles!$B$8*IF(H126="",F126,H126)+Profiles!$B$10*IF(I126="",F126,I126))+Profiles!$C$3*G126)/1000000+Profiles!$D$3*IF(J126="",0,J126)</f>
         <v/>
@@ -9367,27 +9338,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>openai/gpt-5-mini</t>
+          <t>google/gemini-2.5-pro</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr"/>
       <c r="F127" s="9" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="G127" s="9" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H127" s="9" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="I127" s="9" t="n"/>
-      <c r="J127" s="9" t="n"/>
+        <v>0.125</v>
+      </c>
+      <c r="I127" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>1.25e-06</v>
+      </c>
       <c r="K127" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F127+Profiles!$B$8*IF(H127="",F127,H127)+Profiles!$B$10*IF(I127="",F127,I127))+Profiles!$C$3*G127)/1000000+Profiles!$D$3*IF(J127="",0,J127)</f>
         <v/>
@@ -9415,26 +9390,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>openai/gpt-5-nano</t>
+          <t>anthropic/claude-sonnet-4</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2025-08-07</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr"/>
       <c r="F128" s="9" t="n">
-        <v>0.05</v>
+        <v>3</v>
       </c>
       <c r="G128" s="9" t="n">
-        <v>0.4</v>
+        <v>15</v>
       </c>
       <c r="H128" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I128" s="9" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="I128" s="9" t="n">
+        <v>3.75</v>
+      </c>
       <c r="J128" s="9" t="n"/>
       <c r="K128" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F128+Profiles!$B$8*IF(H128="",F128,H128)+Profiles!$B$10*IF(I128="",F128,I128))+Profiles!$C$3*G128)/1000000+Profiles!$D$3*IF(J128="",0,J128)</f>
@@ -9463,28 +9440,26 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>anthropic/claude-opus-4.1</t>
+          <t>mistralai/mistral-medium-3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2025-08-05</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr"/>
       <c r="F129" s="9" t="n">
-        <v>15</v>
+        <v>0.4</v>
       </c>
       <c r="G129" s="9" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="H129" s="9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I129" s="9" t="n">
-        <v>18.75</v>
-      </c>
+        <v>0.04</v>
+      </c>
+      <c r="I129" s="9" t="n"/>
       <c r="J129" s="9" t="n"/>
       <c r="K129" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F129+Profiles!$B$8*IF(H129="",F129,H129)+Profiles!$B$10*IF(I129="",F129,I129))+Profiles!$C$3*G129)/1000000+Profiles!$D$3*IF(J129="",0,J129)</f>
@@ -9513,31 +9488,31 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash-lite</t>
+          <t>openai/o4-mini-high</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>2025-04-16</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>o4-mini with reasoning effort high (kept separate)</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr"/>
       <c r="F130" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>1.1</v>
       </c>
       <c r="G130" s="9" t="n">
-        <v>0.4</v>
+        <v>4.4</v>
       </c>
       <c r="H130" s="9" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I130" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J130" s="9" t="n">
-        <v>1e-07</v>
-      </c>
+        <v>0.275</v>
+      </c>
+      <c r="I130" s="9" t="n"/>
+      <c r="J130" s="9" t="n"/>
       <c r="K130" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F130+Profiles!$B$8*IF(H130="",F130,H130)+Profiles!$B$10*IF(I130="",F130,I130))+Profiles!$C$3*G130)/1000000+Profiles!$D$3*IF(J130="",0,J130)</f>
         <v/>
@@ -9565,23 +9540,25 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-3.2-24b-instruct</t>
+          <t>openai/o3</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr"/>
       <c r="F131" s="9" t="n">
-        <v>0.09375</v>
+        <v>2</v>
       </c>
       <c r="G131" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H131" s="9" t="n"/>
+        <v>8</v>
+      </c>
+      <c r="H131" s="9" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I131" s="9" t="n"/>
       <c r="J131" s="9" t="n"/>
       <c r="K131" s="10">
@@ -9611,31 +9588,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-flash</t>
+          <t>openai/o4-mini</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
       <c r="F132" s="9" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="G132" s="9" t="n">
-        <v>2.5</v>
+        <v>4.4</v>
       </c>
       <c r="H132" s="9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I132" s="9" t="n">
-        <v>0.0833333333333333</v>
-      </c>
-      <c r="J132" s="9" t="n">
-        <v>3e-07</v>
-      </c>
+        <v>0.275</v>
+      </c>
+      <c r="I132" s="9" t="n"/>
+      <c r="J132" s="9" t="n"/>
       <c r="K132" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F132+Profiles!$B$8*IF(H132="",F132,H132)+Profiles!$B$10*IF(I132="",F132,I132))+Profiles!$C$3*G132)/1000000+Profiles!$D$3*IF(J132="",0,J132)</f>
         <v/>
@@ -9663,31 +9636,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-pro</t>
+          <t>openai/gpt-4.1</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr"/>
       <c r="F133" s="9" t="n">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="G133" s="9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H133" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I133" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J133" s="9" t="n">
-        <v>1.25e-06</v>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="I133" s="9" t="n"/>
+      <c r="J133" s="9" t="n"/>
       <c r="K133" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F133+Profiles!$B$8*IF(H133="",F133,H133)+Profiles!$B$10*IF(I133="",F133,I133))+Profiles!$C$3*G133)/1000000+Profiles!$D$3*IF(J133="",0,J133)</f>
         <v/>
@@ -9715,31 +9684,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>google/gemini-2.5-pro-preview</t>
+          <t>openai/gpt-4.1-mini</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2025-06-05</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
       <c r="F134" s="9" t="n">
-        <v>1.25</v>
+        <v>0.4</v>
       </c>
       <c r="G134" s="9" t="n">
-        <v>10</v>
+        <v>1.6</v>
       </c>
       <c r="H134" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I134" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="J134" s="9" t="n">
-        <v>1.25e-06</v>
-      </c>
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="I134" s="9" t="n"/>
+      <c r="J134" s="9" t="n"/>
       <c r="K134" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F134+Profiles!$B$8*IF(H134="",F134,H134)+Profiles!$B$10*IF(I134="",F134,I134))+Profiles!$C$3*G134)/1000000+Profiles!$D$3*IF(J134="",0,J134)</f>
         <v/>
@@ -9767,28 +9732,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>anthropic/claude-sonnet-4</t>
+          <t>openai/gpt-4.1-nano</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr"/>
       <c r="F135" s="9" t="n">
-        <v>3</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="G135" s="9" t="n">
-        <v>15</v>
+        <v>0.4</v>
       </c>
       <c r="H135" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I135" s="9" t="n">
-        <v>3.75</v>
-      </c>
+        <v>0.025</v>
+      </c>
+      <c r="I135" s="9" t="n"/>
       <c r="J135" s="9" t="n"/>
       <c r="K135" s="10">
         <f>(Profiles!$B$3*(Profiles!$B$9*F135+Profiles!$B$8*IF(H135="",F135,H135)+Profiles!$B$10*IF(I135="",F135,I135))+Profiles!$C$3*G135)/1000000+Profiles!$D$3*IF(J135="",0,J135)</f>
@@ -9817,25 +9780,23 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>mistralai/mistral-medium-3</t>
+          <t>meta-llama/llama-4-maverick</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
       <c r="F136" s="9" t="n">
-        <v>0.4</v>
+        <v>0.1875</v>
       </c>
       <c r="G136" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H136" s="9" t="n">
-        <v>0.04</v>
-      </c>
+        <v>0.6525</v>
+      </c>
+      <c r="H136" s="9" t="n"/>
       <c r="I136" s="9" t="n"/>
       <c r="J136" s="9" t="n"/>
       <c r="K136" s="10">
@@ -9865,25 +9826,23 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>openai/o4-mini-high</t>
+          <t>meta-llama/llama-4-scout</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr"/>
       <c r="F137" s="9" t="n">
-        <v>1.1</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="G137" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H137" s="9" t="n">
-        <v>0.275</v>
-      </c>
+        <v>0.3</v>
+      </c>
+      <c r="H137" s="9" t="n"/>
       <c r="I137" s="9" t="n"/>
       <c r="J137" s="9" t="n"/>
       <c r="K137" s="10">
@@ -9913,25 +9872,23 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>openai/o3</t>
+          <t>mistralai/mistral-small-3.1-24b-instruct</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr"/>
       <c r="F138" s="9" t="n">
-        <v>2</v>
+        <v>0.351</v>
       </c>
       <c r="G138" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="H138" s="9" t="n">
-        <v>0.5</v>
-      </c>
+        <v>0.5549999999999999</v>
+      </c>
+      <c r="H138" s="9" t="n"/>
       <c r="I138" s="9" t="n"/>
       <c r="J138" s="9" t="n"/>
       <c r="K138" s="10">
@@ -9961,25 +9918,23 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>openai/o4-mini</t>
+          <t>google/gemma-3-12b-it</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2025-04-16</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
       <c r="F139" s="9" t="n">
-        <v>1.1</v>
+        <v>0.05</v>
       </c>
       <c r="G139" s="9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="H139" s="9" t="n">
-        <v>0.275</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="H139" s="9" t="n"/>
       <c r="I139" s="9" t="n"/>
       <c r="J139" s="9" t="n"/>
       <c r="K139" s="10">
@@ -10009,24 +9964,24 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1</t>
+          <t>google/gemma-3-27b-it</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-03-12</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr"/>
       <c r="F140" s="9" t="n">
-        <v>2</v>
+        <v>0.08</v>
       </c>
       <c r="G140" s="9" t="n">
-        <v>8</v>
+        <v>0.45</v>
       </c>
       <c r="H140" s="9" t="n">
-        <v>0.5</v>
+        <v>0.04</v>
       </c>
       <c r="I140" s="9" t="n"/>
       <c r="J140" s="9" t="n"/>
@@ -10057,25 +10012,23 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-mini</t>
+          <t>amazon/nova-lite-v1</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr"/>
       <c r="F141" s="9" t="n">
-        <v>0.4</v>
+        <v>0.06</v>
       </c>
       <c r="G141" s="9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="H141" s="9" t="n">
-        <v>0.09999999999999999</v>
-      </c>
+        <v>0.24</v>
+      </c>
+      <c r="H141" s="9" t="n"/>
       <c r="I141" s="9" t="n"/>
       <c r="J141" s="9" t="n"/>
       <c r="K141" s="10">
@@ -10105,25 +10058,23 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>openai/gpt-4.1-nano</t>
+          <t>amazon/nova-pro-v1</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2024-12-05</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr"/>
       <c r="F142" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="G142" s="9" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H142" s="9" t="n">
-        <v>0.025</v>
-      </c>
+        <v>3.2</v>
+      </c>
+      <c r="H142" s="9" t="n"/>
       <c r="I142" s="9" t="n"/>
       <c r="J142" s="9" t="n"/>
       <c r="K142" s="10">
@@ -10153,23 +10104,29 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>meta-llama/llama-4-maverick</t>
+          <t>openai/gpt-4o-2024-11-20</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>last GPT-4o</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr"/>
       <c r="F143" s="9" t="n">
-        <v>0.1875</v>
+        <v>2.5</v>
       </c>
       <c r="G143" s="9" t="n">
-        <v>0.6525</v>
-      </c>
-      <c r="H143" s="9" t="n"/>
+        <v>10</v>
+      </c>
+      <c r="H143" s="9" t="n">
+        <v>1.25</v>
+      </c>
       <c r="I143" s="9" t="n"/>
       <c r="J143" s="9" t="n"/>
       <c r="K143" s="10">
@@ -10199,23 +10156,25 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>meta-llama/llama-4-scout</t>
+          <t>openai/gpt-4o-mini</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
       <c r="F144" s="9" t="n">
-        <v>0.09999999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="G144" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="H144" s="9" t="n"/>
+        <v>0.6</v>
+      </c>
+      <c r="H144" s="9" t="n">
+        <v>0.075</v>
+      </c>
       <c r="I144" s="9" t="n"/>
       <c r="J144" s="9" t="n"/>
       <c r="K144" s="10">
@@ -10245,21 +10204,25 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>mistralai/mistral-small-3.1-24b-instruct</t>
+          <t>openai/gpt-4o-2024-05-13</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
+          <t>2024-05-13</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>first GPT-4o</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr"/>
       <c r="F145" s="9" t="n">
-        <v>0.351</v>
+        <v>5</v>
       </c>
       <c r="G145" s="9" t="n">
-        <v>0.5549999999999999</v>
+        <v>15</v>
       </c>
       <c r="H145" s="9" t="n"/>
       <c r="I145" s="9" t="n"/>
@@ -10291,21 +10254,25 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>google/gemma-3-12b-it</t>
+          <t>openai/gpt-4-turbo</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
+          <t>2024-04-09</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>historical: kept for fun (no cache price)</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr"/>
       <c r="F146" s="9" t="n">
-        <v>0.05</v>
+        <v>10</v>
       </c>
       <c r="G146" s="9" t="n">
-        <v>0.15</v>
+        <v>30</v>
       </c>
       <c r="H146" s="9" t="n"/>
       <c r="I146" s="9" t="n"/>
@@ -10331,555 +10298,35 @@
         <v/>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>google/gemma-3-27b-it</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>2025-03-12</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr"/>
-      <c r="F147" s="9" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="G147" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H147" s="9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I147" s="9" t="n"/>
-      <c r="J147" s="9" t="n"/>
-      <c r="K147" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F147+Profiles!$B$8*IF(H147="",F147,H147)+Profiles!$B$10*IF(I147="",F147,I147))+Profiles!$C$3*G147)/1000000+Profiles!$D$3*IF(J147="",0,J147)</f>
-        <v/>
-      </c>
-      <c r="L147" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F147+Profiles!$B$8*IF(H147="",F147,H147)+Profiles!$B$10*IF(I147="",F147,I147))+Profiles!$C$4*G147)/1000000+Profiles!$D$4*IF(J147="",0,J147)</f>
-        <v/>
-      </c>
-      <c r="M147" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F147+Profiles!$B$8*IF(H147="",F147,H147)+Profiles!$B$10*IF(I147="",F147,I147))+Profiles!$C$5*G147)/1000000+Profiles!$D$5*IF(J147="",0,J147)</f>
-        <v/>
-      </c>
-      <c r="N147" s="10">
-        <f>K147+L147+M147</f>
-        <v/>
-      </c>
-      <c r="O147" s="10">
-        <f>3*N147</f>
-        <v/>
-      </c>
-    </row>
     <row r="148">
-      <c r="A148" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>openai/o1</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>2024-12-17</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G148" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="H148" s="9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I148" s="9" t="n"/>
-      <c r="J148" s="9" t="n"/>
-      <c r="K148" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F148+Profiles!$B$8*IF(H148="",F148,H148)+Profiles!$B$10*IF(I148="",F148,I148))+Profiles!$C$3*G148)/1000000+Profiles!$D$3*IF(J148="",0,J148)</f>
-        <v/>
-      </c>
-      <c r="L148" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F148+Profiles!$B$8*IF(H148="",F148,H148)+Profiles!$B$10*IF(I148="",F148,I148))+Profiles!$C$4*G148)/1000000+Profiles!$D$4*IF(J148="",0,J148)</f>
-        <v/>
-      </c>
-      <c r="M148" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F148+Profiles!$B$8*IF(H148="",F148,H148)+Profiles!$B$10*IF(I148="",F148,I148))+Profiles!$C$5*G148)/1000000+Profiles!$D$5*IF(J148="",0,J148)</f>
-        <v/>
-      </c>
-      <c r="N148" s="10">
-        <f>K148+L148+M148</f>
-        <v/>
-      </c>
-      <c r="O148" s="10">
-        <f>3*N148</f>
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>amazon/nova-lite-v1</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr"/>
-      <c r="F149" s="9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G149" s="9" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H149" s="9" t="n"/>
-      <c r="I149" s="9" t="n"/>
-      <c r="J149" s="9" t="n"/>
-      <c r="K149" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F149+Profiles!$B$8*IF(H149="",F149,H149)+Profiles!$B$10*IF(I149="",F149,I149))+Profiles!$C$3*G149)/1000000+Profiles!$D$3*IF(J149="",0,J149)</f>
-        <v/>
-      </c>
-      <c r="L149" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F149+Profiles!$B$8*IF(H149="",F149,H149)+Profiles!$B$10*IF(I149="",F149,I149))+Profiles!$C$4*G149)/1000000+Profiles!$D$4*IF(J149="",0,J149)</f>
-        <v/>
-      </c>
-      <c r="M149" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F149+Profiles!$B$8*IF(H149="",F149,H149)+Profiles!$B$10*IF(I149="",F149,I149))+Profiles!$C$5*G149)/1000000+Profiles!$D$5*IF(J149="",0,J149)</f>
-        <v/>
-      </c>
-      <c r="N149" s="10">
-        <f>K149+L149+M149</f>
-        <v/>
-      </c>
-      <c r="O149" s="10">
-        <f>3*N149</f>
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>amazon/nova-pro-v1</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>2024-12-05</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr"/>
-      <c r="F150" s="9" t="n">
-        <v>0.7999999999999999</v>
-      </c>
-      <c r="G150" s="9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="H150" s="9" t="n"/>
-      <c r="I150" s="9" t="n"/>
-      <c r="J150" s="9" t="n"/>
-      <c r="K150" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F150+Profiles!$B$8*IF(H150="",F150,H150)+Profiles!$B$10*IF(I150="",F150,I150))+Profiles!$C$3*G150)/1000000+Profiles!$D$3*IF(J150="",0,J150)</f>
-        <v/>
-      </c>
-      <c r="L150" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F150+Profiles!$B$8*IF(H150="",F150,H150)+Profiles!$B$10*IF(I150="",F150,I150))+Profiles!$C$4*G150)/1000000+Profiles!$D$4*IF(J150="",0,J150)</f>
-        <v/>
-      </c>
-      <c r="M150" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F150+Profiles!$B$8*IF(H150="",F150,H150)+Profiles!$B$10*IF(I150="",F150,I150))+Profiles!$C$5*G150)/1000000+Profiles!$D$5*IF(J150="",0,J150)</f>
-        <v/>
-      </c>
-      <c r="N150" s="10">
-        <f>K150+L150+M150</f>
-        <v/>
-      </c>
-      <c r="O150" s="10">
-        <f>3*N150</f>
-        <v/>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>150</v>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>openai/gpt-4o-2024-11-20</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>2024-11-20</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr"/>
-      <c r="F151" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G151" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H151" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I151" s="9" t="n"/>
-      <c r="J151" s="9" t="n"/>
-      <c r="K151" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F151+Profiles!$B$8*IF(H151="",F151,H151)+Profiles!$B$10*IF(I151="",F151,I151))+Profiles!$C$3*G151)/1000000+Profiles!$D$3*IF(J151="",0,J151)</f>
-        <v/>
-      </c>
-      <c r="L151" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F151+Profiles!$B$8*IF(H151="",F151,H151)+Profiles!$B$10*IF(I151="",F151,I151))+Profiles!$C$4*G151)/1000000+Profiles!$D$4*IF(J151="",0,J151)</f>
-        <v/>
-      </c>
-      <c r="M151" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F151+Profiles!$B$8*IF(H151="",F151,H151)+Profiles!$B$10*IF(I151="",F151,I151))+Profiles!$C$5*G151)/1000000+Profiles!$D$5*IF(J151="",0,J151)</f>
-        <v/>
-      </c>
-      <c r="N151" s="10">
-        <f>K151+L151+M151</f>
-        <v/>
-      </c>
-      <c r="O151" s="10">
-        <f>3*N151</f>
-        <v/>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>151</v>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>openai/gpt-4o-2024-08-06</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>2024-08-06</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G152" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H152" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I152" s="9" t="n"/>
-      <c r="J152" s="9" t="n"/>
-      <c r="K152" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F152+Profiles!$B$8*IF(H152="",F152,H152)+Profiles!$B$10*IF(I152="",F152,I152))+Profiles!$C$3*G152)/1000000+Profiles!$D$3*IF(J152="",0,J152)</f>
-        <v/>
-      </c>
-      <c r="L152" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F152+Profiles!$B$8*IF(H152="",F152,H152)+Profiles!$B$10*IF(I152="",F152,I152))+Profiles!$C$4*G152)/1000000+Profiles!$D$4*IF(J152="",0,J152)</f>
-        <v/>
-      </c>
-      <c r="M152" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F152+Profiles!$B$8*IF(H152="",F152,H152)+Profiles!$B$10*IF(I152="",F152,I152))+Profiles!$C$5*G152)/1000000+Profiles!$D$5*IF(J152="",0,J152)</f>
-        <v/>
-      </c>
-      <c r="N152" s="10">
-        <f>K152+L152+M152</f>
-        <v/>
-      </c>
-      <c r="O152" s="10">
-        <f>3*N152</f>
-        <v/>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>152</v>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>openai/gpt-4o-mini</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr"/>
-      <c r="F153" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G153" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H153" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I153" s="9" t="n"/>
-      <c r="J153" s="9" t="n"/>
-      <c r="K153" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F153+Profiles!$B$8*IF(H153="",F153,H153)+Profiles!$B$10*IF(I153="",F153,I153))+Profiles!$C$3*G153)/1000000+Profiles!$D$3*IF(J153="",0,J153)</f>
-        <v/>
-      </c>
-      <c r="L153" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F153+Profiles!$B$8*IF(H153="",F153,H153)+Profiles!$B$10*IF(I153="",F153,I153))+Profiles!$C$4*G153)/1000000+Profiles!$D$4*IF(J153="",0,J153)</f>
-        <v/>
-      </c>
-      <c r="M153" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F153+Profiles!$B$8*IF(H153="",F153,H153)+Profiles!$B$10*IF(I153="",F153,I153))+Profiles!$C$5*G153)/1000000+Profiles!$D$5*IF(J153="",0,J153)</f>
-        <v/>
-      </c>
-      <c r="N153" s="10">
-        <f>K153+L153+M153</f>
-        <v/>
-      </c>
-      <c r="O153" s="10">
-        <f>3*N153</f>
-        <v/>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>153</v>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>openai/gpt-4o-mini-2024-07-18</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr"/>
-      <c r="F154" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G154" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H154" s="9" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I154" s="9" t="n"/>
-      <c r="J154" s="9" t="n"/>
-      <c r="K154" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F154+Profiles!$B$8*IF(H154="",F154,H154)+Profiles!$B$10*IF(I154="",F154,I154))+Profiles!$C$3*G154)/1000000+Profiles!$D$3*IF(J154="",0,J154)</f>
-        <v/>
-      </c>
-      <c r="L154" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F154+Profiles!$B$8*IF(H154="",F154,H154)+Profiles!$B$10*IF(I154="",F154,I154))+Profiles!$C$4*G154)/1000000+Profiles!$D$4*IF(J154="",0,J154)</f>
-        <v/>
-      </c>
-      <c r="M154" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F154+Profiles!$B$8*IF(H154="",F154,H154)+Profiles!$B$10*IF(I154="",F154,I154))+Profiles!$C$5*G154)/1000000+Profiles!$D$5*IF(J154="",0,J154)</f>
-        <v/>
-      </c>
-      <c r="N154" s="10">
-        <f>K154+L154+M154</f>
-        <v/>
-      </c>
-      <c r="O154" s="10">
-        <f>3*N154</f>
-        <v/>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>154</v>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>openai/gpt-4o</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr"/>
-      <c r="F155" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G155" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H155" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="I155" s="9" t="n"/>
-      <c r="J155" s="9" t="n"/>
-      <c r="K155" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F155+Profiles!$B$8*IF(H155="",F155,H155)+Profiles!$B$10*IF(I155="",F155,I155))+Profiles!$C$3*G155)/1000000+Profiles!$D$3*IF(J155="",0,J155)</f>
-        <v/>
-      </c>
-      <c r="L155" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F155+Profiles!$B$8*IF(H155="",F155,H155)+Profiles!$B$10*IF(I155="",F155,I155))+Profiles!$C$4*G155)/1000000+Profiles!$D$4*IF(J155="",0,J155)</f>
-        <v/>
-      </c>
-      <c r="M155" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F155+Profiles!$B$8*IF(H155="",F155,H155)+Profiles!$B$10*IF(I155="",F155,I155))+Profiles!$C$5*G155)/1000000+Profiles!$D$5*IF(J155="",0,J155)</f>
-        <v/>
-      </c>
-      <c r="N155" s="10">
-        <f>K155+L155+M155</f>
-        <v/>
-      </c>
-      <c r="O155" s="10">
-        <f>3*N155</f>
-        <v/>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>155</v>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>openai/gpt-4o-2024-05-13</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>2024-05-13</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="G156" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H156" s="9" t="n"/>
-      <c r="I156" s="9" t="n"/>
-      <c r="J156" s="9" t="n"/>
-      <c r="K156" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F156+Profiles!$B$8*IF(H156="",F156,H156)+Profiles!$B$10*IF(I156="",F156,I156))+Profiles!$C$3*G156)/1000000+Profiles!$D$3*IF(J156="",0,J156)</f>
-        <v/>
-      </c>
-      <c r="L156" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F156+Profiles!$B$8*IF(H156="",F156,H156)+Profiles!$B$10*IF(I156="",F156,I156))+Profiles!$C$4*G156)/1000000+Profiles!$D$4*IF(J156="",0,J156)</f>
-        <v/>
-      </c>
-      <c r="M156" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F156+Profiles!$B$8*IF(H156="",F156,H156)+Profiles!$B$10*IF(I156="",F156,I156))+Profiles!$C$5*G156)/1000000+Profiles!$D$5*IF(J156="",0,J156)</f>
-        <v/>
-      </c>
-      <c r="N156" s="10">
-        <f>K156+L156+M156</f>
-        <v/>
-      </c>
-      <c r="O156" s="10">
-        <f>3*N156</f>
-        <v/>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>156</v>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>openai/gpt-4-turbo</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>2024-04-09</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr"/>
-      <c r="F157" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G157" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="H157" s="9" t="n"/>
-      <c r="I157" s="9" t="n"/>
-      <c r="J157" s="9" t="n"/>
-      <c r="K157" s="10">
-        <f>(Profiles!$B$3*(Profiles!$B$9*F157+Profiles!$B$8*IF(H157="",F157,H157)+Profiles!$B$10*IF(I157="",F157,I157))+Profiles!$C$3*G157)/1000000+Profiles!$D$3*IF(J157="",0,J157)</f>
-        <v/>
-      </c>
-      <c r="L157" s="10">
-        <f>(Profiles!$B$4*(Profiles!$B$9*F157+Profiles!$B$8*IF(H157="",F157,H157)+Profiles!$B$10*IF(I157="",F157,I157))+Profiles!$C$4*G157)/1000000+Profiles!$D$4*IF(J157="",0,J157)</f>
-        <v/>
-      </c>
-      <c r="M157" s="10">
-        <f>(Profiles!$B$5*(Profiles!$B$9*F157+Profiles!$B$8*IF(H157="",F157,H157)+Profiles!$B$10*IF(I157="",F157,I157))+Profiles!$C$5*G157)/1000000+Profiles!$D$5*IF(J157="",0,J157)</f>
-        <v/>
-      </c>
-      <c r="N157" s="10">
-        <f>K157+L157+M157</f>
-        <v/>
-      </c>
-      <c r="O157" s="10">
-        <f>3*N157</f>
-        <v/>
-      </c>
-    </row>
-    <row r="159">
-      <c r="B159" s="4" t="inlineStr">
+      <c r="B148" s="4" t="inlineStr">
         <is>
           <t>total</t>
         </is>
       </c>
-      <c r="K159" s="11">
-        <f>SUM(K2:K157)</f>
-        <v/>
-      </c>
-      <c r="L159" s="11">
-        <f>SUM(L2:L157)</f>
-        <v/>
-      </c>
-      <c r="M159" s="11">
-        <f>SUM(M2:M157)</f>
-        <v/>
-      </c>
-      <c r="N159" s="11">
-        <f>SUM(N2:N157)</f>
-        <v/>
-      </c>
-      <c r="O159" s="11">
-        <f>SUM(O2:O157)</f>
+      <c r="K148" s="11">
+        <f>SUM(K2:K146)</f>
+        <v/>
+      </c>
+      <c r="L148" s="11">
+        <f>SUM(L2:L146)</f>
+        <v/>
+      </c>
+      <c r="M148" s="11">
+        <f>SUM(M2:M146)</f>
+        <v/>
+      </c>
+      <c r="N148" s="11">
+        <f>SUM(N2:N146)</f>
+        <v/>
+      </c>
+      <c r="O148" s="11">
+        <f>SUM(O2:O146)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O157"/>
+  <autoFilter ref="A1:O146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10890,7 +10337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -10912,91 +10359,91 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>google/gemini-3-pro-image</t>
+          <t>google/gemini-2.5-pro-preview</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image-generation model</t>
+          <t>duplicate of google/gemini-2.5-pro</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>openai/gpt-5-pro</t>
+          <t>google/gemini-3-pro-image</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+          <t>image-generation model</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>openai/gpt-5.2-pro</t>
+          <t>google/gemini-3.1-flash-lite-preview</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+          <t>duplicate of google/gemini-3.1-flash-lite</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>openai/gpt-5.4-pro</t>
+          <t>google/gemini-3.1-pro-preview-customtools</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+          <t>duplicate of google/gemini-3.1-pro-preview</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5-pro</t>
+          <t>openai/gpt-4o</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+          <t>duplicate of openai/gpt-4o-2024-05-13 and -2024-11-20 (first and last GPT-4o kept)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-luna-pro</t>
+          <t>openai/gpt-4o-2024-08-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+          <t>duplicate of openai/gpt-4o-2024-05-13 and -2024-11-20 (first and last GPT-4o kept)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-sol-pro</t>
+          <t>openai/gpt-4o-mini-2024-07-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+          <t>duplicate of openai/gpt-4o-mini</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>openai/gpt-5.6-terra-pro</t>
+          <t>openai/gpt-5-pro</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11008,7 +10455,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>openai/gpt-6-astra-pro</t>
+          <t>openai/gpt-5.2-pro</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11020,7 +10467,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>openai/gpt-6-luna-pro</t>
+          <t>openai/gpt-5.4-pro</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11032,7 +10479,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>openai/gpt-6-sol-pro</t>
+          <t>openai/gpt-5.5-pro</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -11044,7 +10491,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>openai/o3-pro</t>
+          <t>openai/gpt-5.6-luna-pro</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -11056,82 +10503,214 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sakana/fugu-max</t>
+          <t>openai/gpt-5.6-sol-pro</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>orchestrator (routes between models)</t>
+          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sakana/fugu-ultra</t>
+          <t>openai/gpt-5.6-terra-pro</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>orchestrator (routes between models)</t>
+          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sakana/fugu-ultra-v2</t>
+          <t>openai/gpt-6-astra-pro</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>orchestrator (routes between models)</t>
+          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sakana/sakana-namazu</t>
+          <t>openai/gpt-6-luna-pro</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Japanese fine-tune of Kimi K2.6</t>
+          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>openai/gpt-5.5</t>
+          <t>openai/gpt-6-sol-pro</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>superseded by GPT-6 (latest list only)</t>
+          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>openai/gpt-chat-latest</t>
+          <t>openai/o1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ChatGPT's rolling alias (latest list only)</t>
+          <t>Pro-like: built to think far longer (about $1,049 a pass at list price)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>openai/o3-pro</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>OpenAI Pro: thinks far longer, costs far more than its list price suggests</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>perceptron/perceptron-mk1.5</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>context too small for a painting session (16K / 36K / 65K): a robotics model</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>qwen/qwen3.5-plus-02-15</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>duplicate of qwen/qwen3.5-plus-20260420</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>rekaai/reka-edge</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>context too small for a painting session (16K / 36K / 65K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sakana/fugu-max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>orchestrator (routes between models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sakana/fugu-ultra</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>orchestrator (routes between models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sakana/fugu-ultra-v2</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>orchestrator (routes between models)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sakana/sakana-namazu</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Japanese fine-tune of Kimi K2.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>z-ai/glm-4.5v</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>context too small for a painting session (16K / 36K / 65K)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>openai/gpt-5.5</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>superseded by GPT-6 (latest list only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>openai/gpt-chat-latest</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ChatGPT's rolling alias (latest list only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>xiaomi/mimo-v2.5</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>older MiMo (latest list only)</t>
         </is>
